--- a/AR-Sample-Ledger.xlsx
+++ b/AR-Sample-Ledger.xlsx
@@ -11,7 +11,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ledger" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calcs" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aging pivot" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Ledger'!$A$1:$R$111</definedName>
@@ -28,7 +27,7 @@
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,15 +63,6 @@
       <b val="1"/>
       <color rgb="001B365D"/>
       <sz val="13"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="001B365D"/>
-      <sz val="18"/>
-    </font>
-    <font>
-      <color rgb="001B365D"/>
-      <sz val="14"/>
     </font>
   </fonts>
   <fills count="3">
@@ -114,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -137,9 +127,6 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -238,129 +225,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Open A/R by aging bucket</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="stacked"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Calcs'!B16</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Calcs'!$A$17:$A$20</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Calcs'!$B$17:$B$20</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Calcs'!C16</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Calcs'!$A$17:$A$20</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Calcs'!$C$17:$C$20</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Dollars</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="&quot;$&quot;#,##0" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Patient vs insurance</a:t>
+              <a:t>Patients scheduled vs not scheduled</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -372,6 +237,11 @@
         <ser>
           <idx val="0"/>
           <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Aging pivot'!B31</f>
+            </strRef>
+          </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
@@ -379,17 +249,18 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Calcs'!$A$6:$A$7</f>
+              <f>'Aging pivot'!$A$32:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Calcs'!$B$6:$B$7</f>
+              <f>'Aging pivot'!$B$32:$B$33</f>
             </numRef>
           </val>
         </ser>
         <dLbls>
-          <showVal val="0"/>
+          <showVal val="1"/>
+          <showCatName val="1"/>
           <showPercent val="1"/>
         </dLbls>
         <firstSliceAng val="0"/>
@@ -404,99 +275,16 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="12"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Accounts by primary bucket</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="bar"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Aging pivot'!D4</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Aging pivot'!$A$5:$A$8</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Aging pivot'!$D$5:$D$8</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>5</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2880000"/>
+    <ext cx="5040000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -506,50 +294,6 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4320000" cy="2880000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="2" name="Chart 2"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>23</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="5400000" cy="2880000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="3" name="Chart 3"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -929,7 +673,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ledger · Calcs · Aging pivot · Dashboard</t>
+          <t>Ledger · Calcs · Aging pivot (tables + pie)</t>
         </is>
       </c>
     </row>
@@ -8420,11 +8164,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
@@ -8636,10 +8380,6 @@
         <f>SUMIF(Ledger!A:A,A14,Ledger!F:F)</f>
         <v/>
       </c>
-      <c r="D14" s="13">
-        <f>SUMIF(Ledger!A:A,A14,Ledger!G:G)</f>
-        <v/>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8655,10 +8395,6 @@
         <f>SUMIF(Ledger!A:A,A15,Ledger!F:F)</f>
         <v/>
       </c>
-      <c r="D15" s="13">
-        <f>SUMIF(Ledger!A:A,A15,Ledger!G:G)</f>
-        <v/>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8674,10 +8410,6 @@
         <f>SUMIF(Ledger!A:A,A16,Ledger!F:F)</f>
         <v/>
       </c>
-      <c r="D16" s="13">
-        <f>SUMIF(Ledger!A:A,A16,Ledger!G:G)</f>
-        <v/>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8693,10 +8425,6 @@
         <f>SUMIF(Ledger!A:A,A17,Ledger!F:F)</f>
         <v/>
       </c>
-      <c r="D17" s="13">
-        <f>SUMIF(Ledger!A:A,A17,Ledger!G:G)</f>
-        <v/>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8712,10 +8440,6 @@
         <f>SUMIF(Ledger!A:A,A18,Ledger!F:F)</f>
         <v/>
       </c>
-      <c r="D18" s="13">
-        <f>SUMIF(Ledger!A:A,A18,Ledger!G:G)</f>
-        <v/>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8731,10 +8455,6 @@
         <f>SUMIF(Ledger!A:A,A19,Ledger!F:F)</f>
         <v/>
       </c>
-      <c r="D19" s="13">
-        <f>SUMIF(Ledger!A:A,A19,Ledger!G:G)</f>
-        <v/>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -8750,10 +8470,6 @@
         <f>SUMIF(Ledger!A:A,A20,Ledger!F:F)</f>
         <v/>
       </c>
-      <c r="D20" s="13">
-        <f>SUMIF(Ledger!A:A,A20,Ledger!G:G)</f>
-        <v/>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -8769,10 +8485,6 @@
         <f>SUMIF(Ledger!A:A,A21,Ledger!F:F)</f>
         <v/>
       </c>
-      <c r="D21" s="13">
-        <f>SUMIF(Ledger!A:A,A21,Ledger!G:G)</f>
-        <v/>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -8788,10 +8500,6 @@
         <f>SUMIF(Ledger!A:A,A22,Ledger!F:F)</f>
         <v/>
       </c>
-      <c r="D22" s="13">
-        <f>SUMIF(Ledger!A:A,A22,Ledger!G:G)</f>
-        <v/>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -8807,10 +8515,6 @@
         <f>SUMIF(Ledger!A:A,A23,Ledger!F:F)</f>
         <v/>
       </c>
-      <c r="D23" s="13">
-        <f>SUMIF(Ledger!A:A,A23,Ledger!G:G)</f>
-        <v/>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -8826,10 +8530,6 @@
         <f>SUMIF(Ledger!A:A,A24,Ledger!F:F)</f>
         <v/>
       </c>
-      <c r="D24" s="13">
-        <f>SUMIF(Ledger!A:A,A24,Ledger!G:G)</f>
-        <v/>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -8845,10 +8545,6 @@
         <f>SUMIF(Ledger!A:A,A25,Ledger!F:F)</f>
         <v/>
       </c>
-      <c r="D25" s="13">
-        <f>SUMIF(Ledger!A:A,A25,Ledger!G:G)</f>
-        <v/>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -8864,10 +8560,6 @@
         <f>SUMIF(Ledger!A:A,A26,Ledger!F:F)</f>
         <v/>
       </c>
-      <c r="D26" s="13">
-        <f>SUMIF(Ledger!A:A,A26,Ledger!G:G)</f>
-        <v/>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -8883,10 +8575,6 @@
         <f>SUMIF(Ledger!A:A,A27,Ledger!F:F)</f>
         <v/>
       </c>
-      <c r="D27" s="13">
-        <f>SUMIF(Ledger!A:A,A27,Ledger!G:G)</f>
-        <v/>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -8904,6 +8592,92 @@
       </c>
       <c r="D28" s="13">
         <f>SUMIF(Ledger!A:A,A28,Ledger!G:G)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Next appointment</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Patients</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Open $</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Share</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="B32">
+        <f>COUNTIF(Ledger!Q2:Q111,"Yes")</f>
+        <v/>
+      </c>
+      <c r="C32" s="13">
+        <f>SUMIF(Ledger!Q2:Q111,"Yes",Ledger!E2:E111)</f>
+        <v/>
+      </c>
+      <c r="D32" s="14">
+        <f>IF($B$34=0,0,B32/$B$34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Not scheduled</t>
+        </is>
+      </c>
+      <c r="B33">
+        <f>COUNTIF(Ledger!Q2:Q111,"No")</f>
+        <v/>
+      </c>
+      <c r="C33" s="13">
+        <f>SUMIF(Ledger!Q2:Q111,"No",Ledger!E2:E111)</f>
+        <v/>
+      </c>
+      <c r="D33" s="14">
+        <f>IF($B$34=0,0,B33/$B$34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B34" s="12">
+        <f>SUM(B32:B33)</f>
+        <v/>
+      </c>
+      <c r="C34" s="16">
+        <f>SUM(C32:C33)</f>
+        <v/>
+      </c>
+      <c r="D34" s="17">
+        <f>SUM(D32:D33)</f>
         <v/>
       </c>
     </row>
@@ -8912,78 +8686,6 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00294BEF"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="18" t="inlineStr">
-        <is>
-          <t>Huddle dashboard</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Total owing</t>
-        </is>
-      </c>
-      <c r="B3" s="19">
-        <f>Calcs!B5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Patient / insurance</t>
-        </is>
-      </c>
-      <c r="B4" s="20">
-        <f>TEXT(Calcs!B6,"$#,##0")&amp;" / "&amp;TEXT(Calcs!B7,"$#,##0")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Patient 90+</t>
-        </is>
-      </c>
-      <c r="B5" s="19">
-        <f>Calcs!B9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>90+ with no next appointment</t>
-        </is>
-      </c>
-      <c r="B6" s="20">
-        <f>Calcs!B12&amp;" accounts · "&amp;TEXT(Calcs!B25,"$#,##0")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/AR-Sample-Ledger.xlsx
+++ b/AR-Sample-Ledger.xlsx
@@ -21,11 +21,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -104,14 +103,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -119,17 +118,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -217,7 +223,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -639,6 +644,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -651,13 +657,14 @@
     <row r="6"/>
     <row r="7"/>
     <row r="8"/>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Snapshot</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="19" t="n">
         <v>46288</v>
       </c>
     </row>
@@ -837,41 +844,41 @@
           <t>P-2001</t>
         </is>
       </c>
-      <c r="C2" s="8" t="n">
+      <c r="C2" s="20" t="n">
         <v>46101</v>
       </c>
-      <c r="D2" s="8" t="n"/>
-      <c r="E2" s="9" t="n">
+      <c r="D2" s="20" t="n"/>
+      <c r="E2" s="21" t="n">
         <v>6.4</v>
       </c>
-      <c r="F2" s="9" t="n">
+      <c r="F2" s="21" t="n">
         <v>6.4</v>
       </c>
-      <c r="G2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="9" t="n">
+      <c r="G2" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="21" t="n">
         <v>6.4</v>
       </c>
-      <c r="L2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" s="9" t="n">
+      <c r="L2" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P2" s="7" t="inlineStr">
@@ -900,44 +907,44 @@
           <t>P-2002</t>
         </is>
       </c>
-      <c r="C3" s="8" t="n">
+      <c r="C3" s="20" t="n">
         <v>45941</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="20">
         <f>TODAY()+54</f>
         <v/>
       </c>
-      <c r="E3" s="9" t="n">
+      <c r="E3" s="21" t="n">
         <v>53.4</v>
       </c>
-      <c r="F3" s="9" t="n">
+      <c r="F3" s="21" t="n">
         <v>53.4</v>
       </c>
-      <c r="G3" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="9" t="n">
+      <c r="G3" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="21" t="n">
         <v>53.4</v>
       </c>
-      <c r="L3" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" s="9" t="n">
+      <c r="L3" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P3" s="7" t="inlineStr">
@@ -966,41 +973,41 @@
           <t>P-2003</t>
         </is>
       </c>
-      <c r="C4" s="8" t="n">
+      <c r="C4" s="20" t="n">
         <v>46131</v>
       </c>
-      <c r="D4" s="8" t="n"/>
-      <c r="E4" s="9" t="n">
+      <c r="D4" s="20" t="n"/>
+      <c r="E4" s="21" t="n">
         <v>36</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="21" t="n">
         <v>36</v>
       </c>
-      <c r="G4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="9" t="n">
+      <c r="G4" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="21" t="n">
         <v>36</v>
       </c>
-      <c r="L4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="9" t="n">
+      <c r="L4" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P4" s="7" t="inlineStr">
@@ -1029,41 +1036,41 @@
           <t>P-2004</t>
         </is>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="20" t="n">
         <v>46020</v>
       </c>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="9" t="n">
+      <c r="D5" s="20" t="n"/>
+      <c r="E5" s="21" t="n">
         <v>18.3</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="21" t="n">
         <v>18.3</v>
       </c>
-      <c r="G5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="9" t="n">
+      <c r="G5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="21" t="n">
         <v>18.3</v>
       </c>
-      <c r="L5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="9" t="n">
+      <c r="L5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P5" s="7" t="inlineStr">
@@ -1092,41 +1099,41 @@
           <t>P-2005</t>
         </is>
       </c>
-      <c r="C6" s="8" t="n">
+      <c r="C6" s="20" t="n">
         <v>45890</v>
       </c>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="9" t="n">
+      <c r="D6" s="20" t="n"/>
+      <c r="E6" s="21" t="n">
         <v>95</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="21" t="n">
         <v>95</v>
       </c>
-      <c r="G6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="9" t="n">
+      <c r="G6" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="21" t="n">
         <v>95</v>
       </c>
-      <c r="L6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="9" t="n">
+      <c r="L6" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P6" s="7" t="inlineStr">
@@ -1155,41 +1162,41 @@
           <t>P-2006</t>
         </is>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="20" t="n">
         <v>45937</v>
       </c>
-      <c r="D7" s="8" t="n"/>
-      <c r="E7" s="9" t="n">
+      <c r="D7" s="20" t="n"/>
+      <c r="E7" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="G7" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="9" t="n">
+      <c r="G7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="L7" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="9" t="n">
+      <c r="L7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
@@ -1218,44 +1225,44 @@
           <t>P-2007</t>
         </is>
       </c>
-      <c r="C8" s="8" t="n">
+      <c r="C8" s="20" t="n">
         <v>45961</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="20">
         <f>TODAY()+29</f>
         <v/>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="21" t="n">
         <v>95</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="21" t="n">
         <v>95</v>
       </c>
-      <c r="G8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="9" t="n">
+      <c r="G8" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="21" t="n">
         <v>95</v>
       </c>
-      <c r="L8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="9" t="n">
+      <c r="L8" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
@@ -1284,41 +1291,41 @@
           <t>P-2008</t>
         </is>
       </c>
-      <c r="C9" s="8" t="n">
+      <c r="C9" s="20" t="n">
         <v>46021</v>
       </c>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="9" t="n">
+      <c r="D9" s="20" t="n"/>
+      <c r="E9" s="21" t="n">
         <v>42.5</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="21" t="n">
         <v>42.5</v>
       </c>
-      <c r="G9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="9" t="n">
+      <c r="G9" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="21" t="n">
         <v>42.5</v>
       </c>
-      <c r="L9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="9" t="n">
+      <c r="L9" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P9" s="7" t="inlineStr">
@@ -1347,41 +1354,41 @@
           <t>P-2009</t>
         </is>
       </c>
-      <c r="C10" s="8" t="n">
+      <c r="C10" s="20" t="n">
         <v>45978</v>
       </c>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="9" t="n">
+      <c r="D10" s="20" t="n"/>
+      <c r="E10" s="21" t="n">
         <v>11</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="21" t="n">
         <v>11</v>
       </c>
-      <c r="G10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="9" t="n">
+      <c r="G10" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="21" t="n">
         <v>11</v>
       </c>
-      <c r="L10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="9" t="n">
+      <c r="L10" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P10" s="7" t="inlineStr">
@@ -1410,41 +1417,41 @@
           <t>P-2010</t>
         </is>
       </c>
-      <c r="C11" s="8" t="n">
+      <c r="C11" s="20" t="n">
         <v>46097</v>
       </c>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="9" t="n">
+      <c r="D11" s="20" t="n"/>
+      <c r="E11" s="21" t="n">
         <v>303</v>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" s="21" t="n">
         <v>303</v>
       </c>
-      <c r="G11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="9" t="n">
+      <c r="G11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="21" t="n">
         <v>303</v>
       </c>
-      <c r="L11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="9" t="n">
+      <c r="L11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P11" s="7" t="inlineStr">
@@ -1473,41 +1480,41 @@
           <t>P-2006</t>
         </is>
       </c>
-      <c r="C12" s="8" t="n">
+      <c r="C12" s="20" t="n">
         <v>45937</v>
       </c>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="9" t="n">
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="21" t="n">
         <v>24</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="21" t="n">
         <v>24</v>
       </c>
-      <c r="G12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="9" t="n">
+      <c r="G12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="21" t="n">
         <v>24</v>
       </c>
-      <c r="L12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="9" t="n">
+      <c r="L12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P12" s="7" t="inlineStr">
@@ -1536,41 +1543,41 @@
           <t>P-2011</t>
         </is>
       </c>
-      <c r="C13" s="8" t="n">
+      <c r="C13" s="20" t="n">
         <v>46122</v>
       </c>
-      <c r="D13" s="8" t="n"/>
-      <c r="E13" s="9" t="n">
+      <c r="D13" s="20" t="n"/>
+      <c r="E13" s="21" t="n">
         <v>137.5</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="21" t="n">
         <v>137.5</v>
       </c>
-      <c r="G13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="9" t="n">
+      <c r="G13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="21" t="n">
         <v>137.5</v>
       </c>
-      <c r="L13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="9" t="n">
+      <c r="L13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P13" s="7" t="inlineStr">
@@ -1599,41 +1606,41 @@
           <t>P-2012</t>
         </is>
       </c>
-      <c r="C14" s="8" t="n">
+      <c r="C14" s="20" t="n">
         <v>45917</v>
       </c>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="9" t="n">
+      <c r="D14" s="20" t="n"/>
+      <c r="E14" s="21" t="n">
         <v>40</v>
       </c>
-      <c r="F14" s="9" t="n">
+      <c r="F14" s="21" t="n">
         <v>40</v>
       </c>
-      <c r="G14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="9" t="n">
+      <c r="G14" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="21" t="n">
         <v>40</v>
       </c>
-      <c r="L14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="9" t="n">
+      <c r="L14" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P14" s="7" t="inlineStr">
@@ -1662,41 +1669,41 @@
           <t>P-2003</t>
         </is>
       </c>
-      <c r="C15" s="8" t="n">
+      <c r="C15" s="20" t="n">
         <v>46131</v>
       </c>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="9" t="n">
+      <c r="D15" s="20" t="n"/>
+      <c r="E15" s="21" t="n">
         <v>15</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="21" t="n">
         <v>15</v>
       </c>
-      <c r="G15" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="9" t="n">
+      <c r="G15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="21" t="n">
         <v>15</v>
       </c>
-      <c r="L15" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="9" t="n">
+      <c r="L15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P15" s="7" t="inlineStr">
@@ -1725,41 +1732,41 @@
           <t>P-2013</t>
         </is>
       </c>
-      <c r="C16" s="8" t="n">
+      <c r="C16" s="20" t="n">
         <v>46152</v>
       </c>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="9" t="n">
+      <c r="D16" s="20" t="n"/>
+      <c r="E16" s="21" t="n">
         <v>39.6</v>
       </c>
-      <c r="F16" s="9" t="n">
+      <c r="F16" s="21" t="n">
         <v>39.6</v>
       </c>
-      <c r="G16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="9" t="n">
+      <c r="G16" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="21" t="n">
         <v>39.6</v>
       </c>
-      <c r="L16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="9" t="n">
+      <c r="L16" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P16" s="7" t="inlineStr">
@@ -1788,41 +1795,41 @@
           <t>P-2014</t>
         </is>
       </c>
-      <c r="C17" s="8" t="n">
+      <c r="C17" s="20" t="n">
         <v>45950</v>
       </c>
-      <c r="D17" s="8" t="n"/>
-      <c r="E17" s="9" t="n">
+      <c r="D17" s="20" t="n"/>
+      <c r="E17" s="21" t="n">
         <v>61</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="21" t="n">
         <v>61</v>
       </c>
-      <c r="G17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="9" t="n">
+      <c r="G17" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="21" t="n">
         <v>61</v>
       </c>
-      <c r="L17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="9" t="n">
+      <c r="L17" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P17" s="7" t="inlineStr">
@@ -1851,44 +1858,44 @@
           <t>P-2015</t>
         </is>
       </c>
-      <c r="C18" s="8" t="n">
+      <c r="C18" s="20" t="n">
         <v>46022</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="20">
         <f>TODAY()+29</f>
         <v/>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="E18" s="21" t="n">
         <v>40.05</v>
       </c>
-      <c r="F18" s="9" t="n">
+      <c r="F18" s="21" t="n">
         <v>40.05</v>
       </c>
-      <c r="G18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="9" t="n">
+      <c r="G18" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="21" t="n">
         <v>40.05</v>
       </c>
-      <c r="L18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="9" t="n">
+      <c r="L18" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P18" s="7" t="inlineStr">
@@ -1917,41 +1924,41 @@
           <t>P-2016</t>
         </is>
       </c>
-      <c r="C19" s="8" t="n">
+      <c r="C19" s="20" t="n">
         <v>45984</v>
       </c>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="9" t="n">
+      <c r="D19" s="20" t="n"/>
+      <c r="E19" s="21" t="n">
         <v>83.2</v>
       </c>
-      <c r="F19" s="9" t="n">
+      <c r="F19" s="21" t="n">
         <v>83.2</v>
       </c>
-      <c r="G19" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="9" t="n">
+      <c r="G19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="21" t="n">
         <v>83.2</v>
       </c>
-      <c r="L19" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="9" t="n">
+      <c r="L19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P19" s="7" t="inlineStr">
@@ -1980,44 +1987,44 @@
           <t>P-2017</t>
         </is>
       </c>
-      <c r="C20" s="8" t="n">
+      <c r="C20" s="20" t="n">
         <v>45942</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="20">
         <f>TODAY()+23</f>
         <v/>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="F20" s="9" t="n">
+      <c r="F20" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="G20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="9" t="n">
+      <c r="G20" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="L20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="9" t="n">
+      <c r="L20" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P20" s="7" t="inlineStr">
@@ -2046,44 +2053,44 @@
           <t>P-2007</t>
         </is>
       </c>
-      <c r="C21" s="8" t="n">
+      <c r="C21" s="20" t="n">
         <v>45961</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="20">
         <f>TODAY()+29</f>
         <v/>
       </c>
-      <c r="E21" s="9" t="n">
+      <c r="E21" s="21" t="n">
         <v>195</v>
       </c>
-      <c r="F21" s="9" t="n">
+      <c r="F21" s="21" t="n">
         <v>195</v>
       </c>
-      <c r="G21" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="9" t="n">
+      <c r="G21" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="21" t="n">
         <v>195</v>
       </c>
-      <c r="L21" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="9" t="n">
+      <c r="L21" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P21" s="7" t="inlineStr">
@@ -2112,44 +2119,44 @@
           <t>P-2018</t>
         </is>
       </c>
-      <c r="C22" s="8" t="n">
+      <c r="C22" s="20" t="n">
         <v>46036</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D22" s="20">
         <f>TODAY()+20</f>
         <v/>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="21" t="n">
         <v>37</v>
       </c>
-      <c r="F22" s="9" t="n">
+      <c r="F22" s="21" t="n">
         <v>37</v>
       </c>
-      <c r="G22" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="9" t="n">
+      <c r="G22" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="21" t="n">
         <v>37</v>
       </c>
-      <c r="L22" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="9" t="n">
+      <c r="L22" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P22" s="7" t="inlineStr">
@@ -2178,44 +2185,44 @@
           <t>P-2019</t>
         </is>
       </c>
-      <c r="C23" s="8" t="n">
+      <c r="C23" s="20" t="n">
         <v>46181</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="20">
         <f>TODAY()+59</f>
         <v/>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E23" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="F23" s="9" t="n">
+      <c r="F23" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="G23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="9" t="n">
+      <c r="G23" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="L23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="9" t="n">
+      <c r="L23" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P23" s="7" t="inlineStr">
@@ -2244,41 +2251,41 @@
           <t>P-2020</t>
         </is>
       </c>
-      <c r="C24" s="8" t="n">
+      <c r="C24" s="20" t="n">
         <v>46008</v>
       </c>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="9" t="n">
+      <c r="D24" s="20" t="n"/>
+      <c r="E24" s="21" t="n">
         <v>109</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F24" s="21" t="n">
         <v>109</v>
       </c>
-      <c r="G24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="9" t="n">
+      <c r="G24" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="21" t="n">
         <v>109</v>
       </c>
-      <c r="L24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="9" t="n">
+      <c r="L24" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P24" s="7" t="inlineStr">
@@ -2307,41 +2314,41 @@
           <t>P-2021</t>
         </is>
       </c>
-      <c r="C25" s="8" t="n">
+      <c r="C25" s="20" t="n">
         <v>46158</v>
       </c>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="9" t="n">
+      <c r="D25" s="20" t="n"/>
+      <c r="E25" s="21" t="n">
         <v>159.7</v>
       </c>
-      <c r="F25" s="9" t="n">
+      <c r="F25" s="21" t="n">
         <v>159.7</v>
       </c>
-      <c r="G25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="9" t="n">
+      <c r="G25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="21" t="n">
         <v>159.7</v>
       </c>
-      <c r="L25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="9" t="n">
+      <c r="L25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P25" s="7" t="inlineStr">
@@ -2370,41 +2377,41 @@
           <t>P-2012</t>
         </is>
       </c>
-      <c r="C26" s="8" t="n">
+      <c r="C26" s="20" t="n">
         <v>45917</v>
       </c>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="9" t="n">
+      <c r="D26" s="20" t="n"/>
+      <c r="E26" s="21" t="n">
         <v>59.6</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F26" s="21" t="n">
         <v>59.6</v>
       </c>
-      <c r="G26" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="9" t="n">
+      <c r="G26" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="21" t="n">
         <v>59.6</v>
       </c>
-      <c r="L26" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="9" t="n">
+      <c r="L26" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P26" s="7" t="inlineStr">
@@ -2433,41 +2440,41 @@
           <t>P-2022</t>
         </is>
       </c>
-      <c r="C27" s="8" t="n">
+      <c r="C27" s="20" t="n">
         <v>45961</v>
       </c>
-      <c r="D27" s="8" t="n"/>
-      <c r="E27" s="9" t="n">
+      <c r="D27" s="20" t="n"/>
+      <c r="E27" s="21" t="n">
         <v>53.4</v>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F27" s="21" t="n">
         <v>53.4</v>
       </c>
-      <c r="G27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="9" t="n">
+      <c r="G27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="21" t="n">
         <v>53.4</v>
       </c>
-      <c r="L27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="9" t="n">
+      <c r="L27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P27" s="7" t="inlineStr">
@@ -2496,44 +2503,44 @@
           <t>P-2023</t>
         </is>
       </c>
-      <c r="C28" s="8" t="n">
+      <c r="C28" s="20" t="n">
         <v>46047</v>
       </c>
-      <c r="D28" s="8">
+      <c r="D28" s="20">
         <f>TODAY()+41</f>
         <v/>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="21" t="n">
         <v>14</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="21" t="n">
         <v>14</v>
       </c>
-      <c r="G28" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="9" t="n">
+      <c r="G28" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="21" t="n">
         <v>14</v>
       </c>
-      <c r="L28" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" s="9" t="n">
+      <c r="L28" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P28" s="7" t="inlineStr">
@@ -2562,44 +2569,44 @@
           <t>P-2024</t>
         </is>
       </c>
-      <c r="C29" s="8" t="n">
+      <c r="C29" s="20" t="n">
         <v>46079</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="20">
         <f>TODAY()+10</f>
         <v/>
       </c>
-      <c r="E29" s="9" t="n">
+      <c r="E29" s="21" t="n">
         <v>1431.34</v>
       </c>
-      <c r="F29" s="9" t="n">
+      <c r="F29" s="21" t="n">
         <v>1431.34</v>
       </c>
-      <c r="G29" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="9" t="n">
+      <c r="G29" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="21" t="n">
         <v>1431.34</v>
       </c>
-      <c r="L29" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="9" t="n">
+      <c r="L29" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P29" s="7" t="inlineStr">
@@ -2628,41 +2635,41 @@
           <t>P-2013</t>
         </is>
       </c>
-      <c r="C30" s="8" t="n">
+      <c r="C30" s="20" t="n">
         <v>46152</v>
       </c>
-      <c r="D30" s="8" t="n"/>
-      <c r="E30" s="9" t="n">
+      <c r="D30" s="20" t="n"/>
+      <c r="E30" s="21" t="n">
         <v>109.6</v>
       </c>
-      <c r="F30" s="9" t="n">
+      <c r="F30" s="21" t="n">
         <v>109.6</v>
       </c>
-      <c r="G30" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="9" t="n">
+      <c r="G30" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="21" t="n">
         <v>109.6</v>
       </c>
-      <c r="L30" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="9" t="n">
+      <c r="L30" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P30" s="7" t="inlineStr">
@@ -2691,41 +2698,41 @@
           <t>P-2025</t>
         </is>
       </c>
-      <c r="C31" s="8" t="n">
+      <c r="C31" s="20" t="n">
         <v>45945</v>
       </c>
-      <c r="D31" s="8" t="n"/>
-      <c r="E31" s="9" t="n">
+      <c r="D31" s="20" t="n"/>
+      <c r="E31" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="F31" s="9" t="n">
+      <c r="F31" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="G31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="9" t="n">
+      <c r="G31" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="L31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="9" t="n">
+      <c r="L31" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P31" s="7" t="inlineStr">
@@ -2754,44 +2761,44 @@
           <t>P-2026</t>
         </is>
       </c>
-      <c r="C32" s="8" t="n">
+      <c r="C32" s="20" t="n">
         <v>46065</v>
       </c>
-      <c r="D32" s="8">
+      <c r="D32" s="20">
         <f>TODAY()+24</f>
         <v/>
       </c>
-      <c r="E32" s="9" t="n">
+      <c r="E32" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="F32" s="9" t="n">
+      <c r="F32" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="G32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="9" t="n">
+      <c r="G32" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="L32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="9" t="n">
+      <c r="L32" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P32" s="7" t="inlineStr">
@@ -2820,41 +2827,41 @@
           <t>P-2027</t>
         </is>
       </c>
-      <c r="C33" s="8" t="n">
+      <c r="C33" s="20" t="n">
         <v>46170</v>
       </c>
-      <c r="D33" s="8" t="n"/>
-      <c r="E33" s="9" t="n">
+      <c r="D33" s="20" t="n"/>
+      <c r="E33" s="21" t="n">
         <v>23</v>
       </c>
-      <c r="F33" s="9" t="n">
+      <c r="F33" s="21" t="n">
         <v>23</v>
       </c>
-      <c r="G33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="9" t="n">
+      <c r="G33" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="21" t="n">
         <v>23</v>
       </c>
-      <c r="L33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="9" t="n">
+      <c r="L33" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P33" s="7" t="inlineStr">
@@ -2883,41 +2890,41 @@
           <t>P-2028</t>
         </is>
       </c>
-      <c r="C34" s="8" t="n">
+      <c r="C34" s="20" t="n">
         <v>45931</v>
       </c>
-      <c r="D34" s="8" t="n"/>
-      <c r="E34" s="9" t="n">
+      <c r="D34" s="20" t="n"/>
+      <c r="E34" s="21" t="n">
         <v>16</v>
       </c>
-      <c r="F34" s="9" t="n">
+      <c r="F34" s="21" t="n">
         <v>16</v>
       </c>
-      <c r="G34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="9" t="n">
+      <c r="G34" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="21" t="n">
         <v>16</v>
       </c>
-      <c r="L34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="9" t="n">
+      <c r="L34" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P34" s="7" t="inlineStr">
@@ -2946,41 +2953,41 @@
           <t>P-2027</t>
         </is>
       </c>
-      <c r="C35" s="8" t="n">
+      <c r="C35" s="20" t="n">
         <v>46170</v>
       </c>
-      <c r="D35" s="8" t="n"/>
-      <c r="E35" s="9" t="n">
+      <c r="D35" s="20" t="n"/>
+      <c r="E35" s="21" t="n">
         <v>6.3</v>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="F35" s="21" t="n">
         <v>6.3</v>
       </c>
-      <c r="G35" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="9" t="n">
+      <c r="G35" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="21" t="n">
         <v>6.3</v>
       </c>
-      <c r="L35" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="9" t="n">
+      <c r="L35" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P35" s="7" t="inlineStr">
@@ -3009,44 +3016,44 @@
           <t>P-2007</t>
         </is>
       </c>
-      <c r="C36" s="8" t="n">
+      <c r="C36" s="20" t="n">
         <v>45961</v>
       </c>
-      <c r="D36" s="8">
+      <c r="D36" s="20">
         <f>TODAY()+29</f>
         <v/>
       </c>
-      <c r="E36" s="9" t="n">
+      <c r="E36" s="21" t="n">
         <v>233</v>
       </c>
-      <c r="F36" s="9" t="n">
+      <c r="F36" s="21" t="n">
         <v>233</v>
       </c>
-      <c r="G36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" s="9" t="n">
+      <c r="G36" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="21" t="n">
         <v>233</v>
       </c>
-      <c r="L36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="9" t="n">
+      <c r="L36" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P36" s="7" t="inlineStr">
@@ -3075,41 +3082,41 @@
           <t>P-2029</t>
         </is>
       </c>
-      <c r="C37" s="8" t="n">
+      <c r="C37" s="20" t="n">
         <v>46067</v>
       </c>
-      <c r="D37" s="8" t="n"/>
-      <c r="E37" s="9" t="n">
+      <c r="D37" s="20" t="n"/>
+      <c r="E37" s="21" t="n">
         <v>103.25</v>
       </c>
-      <c r="F37" s="9" t="n">
+      <c r="F37" s="21" t="n">
         <v>103.25</v>
       </c>
-      <c r="G37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" s="9" t="n">
+      <c r="G37" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="21" t="n">
         <v>103.25</v>
       </c>
-      <c r="L37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" s="9" t="n">
+      <c r="L37" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P37" s="7" t="inlineStr">
@@ -3138,41 +3145,41 @@
           <t>P-2030</t>
         </is>
       </c>
-      <c r="C38" s="8" t="n">
+      <c r="C38" s="20" t="n">
         <v>46048</v>
       </c>
-      <c r="D38" s="8" t="n"/>
-      <c r="E38" s="9" t="n">
+      <c r="D38" s="20" t="n"/>
+      <c r="E38" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="F38" s="9" t="n">
+      <c r="F38" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="G38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" s="9" t="n">
+      <c r="G38" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="L38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" s="9" t="n">
+      <c r="L38" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P38" s="7" t="inlineStr">
@@ -3201,44 +3208,44 @@
           <t>P-2031</t>
         </is>
       </c>
-      <c r="C39" s="8" t="n">
+      <c r="C39" s="20" t="n">
         <v>45906</v>
       </c>
-      <c r="D39" s="8">
+      <c r="D39" s="20">
         <f>TODAY()+8</f>
         <v/>
       </c>
-      <c r="E39" s="9" t="n">
+      <c r="E39" s="21" t="n">
         <v>16</v>
       </c>
-      <c r="F39" s="9" t="n">
+      <c r="F39" s="21" t="n">
         <v>16</v>
       </c>
-      <c r="G39" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="9" t="n">
+      <c r="G39" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="21" t="n">
         <v>16</v>
       </c>
-      <c r="L39" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="9" t="n">
+      <c r="L39" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P39" s="7" t="inlineStr">
@@ -3267,41 +3274,41 @@
           <t>P-2032</t>
         </is>
       </c>
-      <c r="C40" s="8" t="n">
+      <c r="C40" s="20" t="n">
         <v>46141</v>
       </c>
-      <c r="D40" s="8" t="n"/>
-      <c r="E40" s="9" t="n">
+      <c r="D40" s="20" t="n"/>
+      <c r="E40" s="21" t="n">
         <v>2226.15</v>
       </c>
-      <c r="F40" s="9" t="n">
+      <c r="F40" s="21" t="n">
         <v>1228.78</v>
       </c>
-      <c r="G40" s="9" t="n">
+      <c r="G40" s="21" t="n">
         <v>997.37</v>
       </c>
-      <c r="H40" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" s="9" t="n">
+      <c r="H40" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="21" t="n">
         <v>1228.78</v>
       </c>
-      <c r="L40" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="9" t="n">
+      <c r="L40" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="21" t="n">
         <v>997.37</v>
       </c>
       <c r="P40" s="7" t="inlineStr">
@@ -3330,41 +3337,41 @@
           <t>P-2033</t>
         </is>
       </c>
-      <c r="C41" s="8" t="n">
+      <c r="C41" s="20" t="n">
         <v>46020</v>
       </c>
-      <c r="D41" s="8" t="n"/>
-      <c r="E41" s="9" t="n">
+      <c r="D41" s="20" t="n"/>
+      <c r="E41" s="21" t="n">
         <v>15</v>
       </c>
-      <c r="F41" s="9" t="n">
+      <c r="F41" s="21" t="n">
         <v>15</v>
       </c>
-      <c r="G41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="9" t="n">
+      <c r="G41" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="21" t="n">
         <v>15</v>
       </c>
-      <c r="L41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" s="9" t="n">
+      <c r="L41" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P41" s="7" t="inlineStr">
@@ -3393,41 +3400,41 @@
           <t>P-2034</t>
         </is>
       </c>
-      <c r="C42" s="8" t="n">
+      <c r="C42" s="20" t="n">
         <v>45921</v>
       </c>
-      <c r="D42" s="8" t="n"/>
-      <c r="E42" s="9" t="n">
+      <c r="D42" s="20" t="n"/>
+      <c r="E42" s="21" t="n">
         <v>46</v>
       </c>
-      <c r="F42" s="9" t="n">
+      <c r="F42" s="21" t="n">
         <v>46</v>
       </c>
-      <c r="G42" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="9" t="n">
+      <c r="G42" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="21" t="n">
         <v>46</v>
       </c>
-      <c r="L42" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" s="9" t="n">
+      <c r="L42" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P42" s="7" t="inlineStr">
@@ -3456,44 +3463,44 @@
           <t>P-2035</t>
         </is>
       </c>
-      <c r="C43" s="8" t="n">
+      <c r="C43" s="20" t="n">
         <v>45935</v>
       </c>
-      <c r="D43" s="8">
+      <c r="D43" s="20">
         <f>TODAY()+54</f>
         <v/>
       </c>
-      <c r="E43" s="9" t="n">
+      <c r="E43" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="F43" s="9" t="n">
+      <c r="F43" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="G43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" s="9" t="n">
+      <c r="G43" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="L43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="9" t="n">
+      <c r="L43" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P43" s="7" t="inlineStr">
@@ -3522,41 +3529,41 @@
           <t>P-2014</t>
         </is>
       </c>
-      <c r="C44" s="8" t="n">
+      <c r="C44" s="20" t="n">
         <v>45950</v>
       </c>
-      <c r="D44" s="8" t="n"/>
-      <c r="E44" s="9" t="n">
+      <c r="D44" s="20" t="n"/>
+      <c r="E44" s="21" t="n">
         <v>72</v>
       </c>
-      <c r="F44" s="9" t="n">
+      <c r="F44" s="21" t="n">
         <v>72</v>
       </c>
-      <c r="G44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" s="9" t="n">
+      <c r="G44" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="21" t="n">
         <v>72</v>
       </c>
-      <c r="L44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" s="9" t="n">
+      <c r="L44" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P44" s="7" t="inlineStr">
@@ -3585,41 +3592,41 @@
           <t>P-2036</t>
         </is>
       </c>
-      <c r="C45" s="8" t="n">
+      <c r="C45" s="20" t="n">
         <v>45893</v>
       </c>
-      <c r="D45" s="8" t="n"/>
-      <c r="E45" s="9" t="n">
+      <c r="D45" s="20" t="n"/>
+      <c r="E45" s="21" t="n">
         <v>2.6</v>
       </c>
-      <c r="F45" s="9" t="n">
+      <c r="F45" s="21" t="n">
         <v>2.6</v>
       </c>
-      <c r="G45" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" s="9" t="n">
+      <c r="G45" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="21" t="n">
         <v>2.6</v>
       </c>
-      <c r="L45" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" s="9" t="n">
+      <c r="L45" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P45" s="7" t="inlineStr">
@@ -3648,44 +3655,44 @@
           <t>P-2023</t>
         </is>
       </c>
-      <c r="C46" s="8" t="n">
+      <c r="C46" s="20" t="n">
         <v>46047</v>
       </c>
-      <c r="D46" s="8">
+      <c r="D46" s="20">
         <f>TODAY()+41</f>
         <v/>
       </c>
-      <c r="E46" s="9" t="n">
+      <c r="E46" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="F46" s="9" t="n">
+      <c r="F46" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="G46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" s="9" t="n">
+      <c r="G46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="L46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" s="9" t="n">
+      <c r="L46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P46" s="7" t="inlineStr">
@@ -3714,44 +3721,44 @@
           <t>P-2024</t>
         </is>
       </c>
-      <c r="C47" s="8" t="n">
+      <c r="C47" s="20" t="n">
         <v>46079</v>
       </c>
-      <c r="D47" s="8">
+      <c r="D47" s="20">
         <f>TODAY()+10</f>
         <v/>
       </c>
-      <c r="E47" s="9" t="n">
+      <c r="E47" s="21" t="n">
         <v>108.6</v>
       </c>
-      <c r="F47" s="9" t="n">
+      <c r="F47" s="21" t="n">
         <v>108.6</v>
       </c>
-      <c r="G47" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" s="9" t="n">
+      <c r="G47" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="21" t="n">
         <v>108.6</v>
       </c>
-      <c r="L47" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" s="9" t="n">
+      <c r="L47" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P47" s="7" t="inlineStr">
@@ -3780,41 +3787,41 @@
           <t>P-2013</t>
         </is>
       </c>
-      <c r="C48" s="8" t="n">
+      <c r="C48" s="20" t="n">
         <v>46152</v>
       </c>
-      <c r="D48" s="8" t="n"/>
-      <c r="E48" s="9" t="n">
+      <c r="D48" s="20" t="n"/>
+      <c r="E48" s="21" t="n">
         <v>138</v>
       </c>
-      <c r="F48" s="9" t="n">
+      <c r="F48" s="21" t="n">
         <v>138</v>
       </c>
-      <c r="G48" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" s="9" t="n">
+      <c r="G48" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="21" t="n">
         <v>138</v>
       </c>
-      <c r="L48" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" s="9" t="n">
+      <c r="L48" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P48" s="7" t="inlineStr">
@@ -3843,41 +3850,41 @@
           <t>P-2037</t>
         </is>
       </c>
-      <c r="C49" s="8" t="n">
+      <c r="C49" s="20" t="n">
         <v>46010</v>
       </c>
-      <c r="D49" s="8" t="n"/>
-      <c r="E49" s="9" t="n">
+      <c r="D49" s="20" t="n"/>
+      <c r="E49" s="21" t="n">
         <v>366</v>
       </c>
-      <c r="F49" s="9" t="n">
+      <c r="F49" s="21" t="n">
         <v>366</v>
       </c>
-      <c r="G49" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="9" t="n">
+      <c r="G49" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="21" t="n">
         <v>366</v>
       </c>
-      <c r="L49" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" s="9" t="n">
+      <c r="L49" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P49" s="7" t="inlineStr">
@@ -3906,41 +3913,41 @@
           <t>P-2038</t>
         </is>
       </c>
-      <c r="C50" s="8" t="n">
+      <c r="C50" s="20" t="n">
         <v>46189</v>
       </c>
-      <c r="D50" s="8" t="n"/>
-      <c r="E50" s="9" t="n">
+      <c r="D50" s="20" t="n"/>
+      <c r="E50" s="21" t="n">
         <v>984</v>
       </c>
-      <c r="F50" s="9" t="n">
+      <c r="F50" s="21" t="n">
         <v>984</v>
       </c>
-      <c r="G50" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" s="9" t="n">
+      <c r="G50" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="21" t="n">
         <v>984</v>
       </c>
-      <c r="L50" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" s="9" t="n">
+      <c r="L50" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P50" s="7" t="inlineStr">
@@ -3969,44 +3976,44 @@
           <t>P-2039</t>
         </is>
       </c>
-      <c r="C51" s="8" t="n">
+      <c r="C51" s="20" t="n">
         <v>45956</v>
       </c>
-      <c r="D51" s="8">
+      <c r="D51" s="20">
         <f>TODAY()+65</f>
         <v/>
       </c>
-      <c r="E51" s="9" t="n">
+      <c r="E51" s="21" t="n">
         <v>50</v>
       </c>
-      <c r="F51" s="9" t="n">
+      <c r="F51" s="21" t="n">
         <v>50</v>
       </c>
-      <c r="G51" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" s="9" t="n">
+      <c r="G51" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="21" t="n">
         <v>50</v>
       </c>
-      <c r="L51" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" s="9" t="n">
+      <c r="L51" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P51" s="7" t="inlineStr">
@@ -4035,41 +4042,41 @@
           <t>P-2040</t>
         </is>
       </c>
-      <c r="C52" s="8" t="n">
+      <c r="C52" s="20" t="n">
         <v>45901</v>
       </c>
-      <c r="D52" s="8" t="n"/>
-      <c r="E52" s="9" t="n">
+      <c r="D52" s="20" t="n"/>
+      <c r="E52" s="21" t="n">
         <v>28.4</v>
       </c>
-      <c r="F52" s="9" t="n">
+      <c r="F52" s="21" t="n">
         <v>28.4</v>
       </c>
-      <c r="G52" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" s="9" t="n">
+      <c r="G52" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="21" t="n">
         <v>28.4</v>
       </c>
-      <c r="L52" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" s="9" t="n">
+      <c r="L52" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P52" s="7" t="inlineStr">
@@ -4098,41 +4105,41 @@
           <t>P-2041</t>
         </is>
       </c>
-      <c r="C53" s="8" t="n">
+      <c r="C53" s="20" t="n">
         <v>45983</v>
       </c>
-      <c r="D53" s="8" t="n"/>
-      <c r="E53" s="9" t="n">
+      <c r="D53" s="20" t="n"/>
+      <c r="E53" s="21" t="n">
         <v>277</v>
       </c>
-      <c r="F53" s="9" t="n">
+      <c r="F53" s="21" t="n">
         <v>277</v>
       </c>
-      <c r="G53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="9" t="n">
+      <c r="G53" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="21" t="n">
         <v>277</v>
       </c>
-      <c r="L53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" s="9" t="n">
+      <c r="L53" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P53" s="7" t="inlineStr">
@@ -4161,41 +4168,41 @@
           <t>P-2042</t>
         </is>
       </c>
-      <c r="C54" s="8" t="n">
+      <c r="C54" s="20" t="n">
         <v>46169</v>
       </c>
-      <c r="D54" s="8" t="n"/>
-      <c r="E54" s="9" t="n">
+      <c r="D54" s="20" t="n"/>
+      <c r="E54" s="21" t="n">
         <v>66</v>
       </c>
-      <c r="F54" s="9" t="n">
+      <c r="F54" s="21" t="n">
         <v>66</v>
       </c>
-      <c r="G54" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="9" t="n">
+      <c r="G54" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="21" t="n">
         <v>66</v>
       </c>
-      <c r="L54" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="9" t="n">
+      <c r="L54" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P54" s="7" t="inlineStr">
@@ -4224,41 +4231,41 @@
           <t>P-2016</t>
         </is>
       </c>
-      <c r="C55" s="8" t="n">
+      <c r="C55" s="20" t="n">
         <v>45984</v>
       </c>
-      <c r="D55" s="8" t="n"/>
-      <c r="E55" s="9" t="n">
+      <c r="D55" s="20" t="n"/>
+      <c r="E55" s="21" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="F55" s="9" t="n">
+      <c r="F55" s="21" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="G55" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" s="9" t="n">
+      <c r="G55" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="21" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="L55" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" s="9" t="n">
+      <c r="L55" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P55" s="7" t="inlineStr">
@@ -4287,41 +4294,41 @@
           <t>P-2043</t>
         </is>
       </c>
-      <c r="C56" s="8" t="n">
+      <c r="C56" s="20" t="n">
         <v>46065</v>
       </c>
-      <c r="D56" s="8" t="n"/>
-      <c r="E56" s="9" t="n">
+      <c r="D56" s="20" t="n"/>
+      <c r="E56" s="21" t="n">
         <v>848.5</v>
       </c>
-      <c r="F56" s="9" t="n">
+      <c r="F56" s="21" t="n">
         <v>848.5</v>
       </c>
-      <c r="G56" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" s="9" t="n">
+      <c r="G56" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="21" t="n">
         <v>848.5</v>
       </c>
-      <c r="L56" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="9" t="n">
+      <c r="L56" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P56" s="7" t="inlineStr">
@@ -4350,44 +4357,44 @@
           <t>P-2044</t>
         </is>
       </c>
-      <c r="C57" s="8" t="n">
+      <c r="C57" s="20" t="n">
         <v>45898</v>
       </c>
-      <c r="D57" s="8">
+      <c r="D57" s="20">
         <f>TODAY()+23</f>
         <v/>
       </c>
-      <c r="E57" s="9" t="n">
+      <c r="E57" s="21" t="n">
         <v>30.6</v>
       </c>
-      <c r="F57" s="9" t="n">
+      <c r="F57" s="21" t="n">
         <v>30.6</v>
       </c>
-      <c r="G57" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" s="9" t="n">
+      <c r="G57" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="21" t="n">
         <v>30.6</v>
       </c>
-      <c r="L57" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" s="9" t="n">
+      <c r="L57" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P57" s="7" t="inlineStr">
@@ -4416,41 +4423,41 @@
           <t>P-2045</t>
         </is>
       </c>
-      <c r="C58" s="8" t="n">
+      <c r="C58" s="20" t="n">
         <v>46168</v>
       </c>
-      <c r="D58" s="8" t="n"/>
-      <c r="E58" s="9" t="n">
+      <c r="D58" s="20" t="n"/>
+      <c r="E58" s="21" t="n">
         <v>50</v>
       </c>
-      <c r="F58" s="9" t="n">
+      <c r="F58" s="21" t="n">
         <v>50</v>
       </c>
-      <c r="G58" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" s="9" t="n">
+      <c r="G58" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="21" t="n">
         <v>50</v>
       </c>
-      <c r="L58" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="9" t="n">
+      <c r="L58" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P58" s="7" t="inlineStr">
@@ -4479,41 +4486,41 @@
           <t>P-2040</t>
         </is>
       </c>
-      <c r="C59" s="8" t="n">
+      <c r="C59" s="20" t="n">
         <v>45901</v>
       </c>
-      <c r="D59" s="8" t="n"/>
-      <c r="E59" s="9" t="n">
+      <c r="D59" s="20" t="n"/>
+      <c r="E59" s="21" t="n">
         <v>12.4</v>
       </c>
-      <c r="F59" s="9" t="n">
+      <c r="F59" s="21" t="n">
         <v>12.4</v>
       </c>
-      <c r="G59" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" s="9" t="n">
+      <c r="G59" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="21" t="n">
         <v>12.4</v>
       </c>
-      <c r="L59" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" s="9" t="n">
+      <c r="L59" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P59" s="7" t="inlineStr">
@@ -4542,41 +4549,41 @@
           <t>P-2046</t>
         </is>
       </c>
-      <c r="C60" s="8" t="n">
+      <c r="C60" s="20" t="n">
         <v>46020</v>
       </c>
-      <c r="D60" s="8" t="n"/>
-      <c r="E60" s="9" t="n">
+      <c r="D60" s="20" t="n"/>
+      <c r="E60" s="21" t="n">
         <v>0.2</v>
       </c>
-      <c r="F60" s="9" t="n">
+      <c r="F60" s="21" t="n">
         <v>0.2</v>
       </c>
-      <c r="G60" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" s="9" t="n">
+      <c r="G60" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="21" t="n">
         <v>0.2</v>
       </c>
-      <c r="L60" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" s="9" t="n">
+      <c r="L60" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P60" s="7" t="inlineStr">
@@ -4605,44 +4612,44 @@
           <t>P-2047</t>
         </is>
       </c>
-      <c r="C61" s="8" t="n">
+      <c r="C61" s="20" t="n">
         <v>45962</v>
       </c>
-      <c r="D61" s="8">
+      <c r="D61" s="20">
         <f>TODAY()+62</f>
         <v/>
       </c>
-      <c r="E61" s="9" t="n">
+      <c r="E61" s="21" t="n">
         <v>107</v>
       </c>
-      <c r="F61" s="9" t="n">
+      <c r="F61" s="21" t="n">
         <v>107</v>
       </c>
-      <c r="G61" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" s="9" t="n">
+      <c r="G61" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="21" t="n">
         <v>107</v>
       </c>
-      <c r="L61" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" s="9" t="n">
+      <c r="L61" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P61" s="7" t="inlineStr">
@@ -4671,44 +4678,44 @@
           <t>P-2048</t>
         </is>
       </c>
-      <c r="C62" s="8" t="n">
+      <c r="C62" s="20" t="n">
         <v>46262</v>
       </c>
-      <c r="D62" s="8">
+      <c r="D62" s="20">
         <f>TODAY()+18</f>
         <v/>
       </c>
-      <c r="E62" s="9" t="n">
+      <c r="E62" s="21" t="n">
         <v>357</v>
       </c>
-      <c r="F62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" s="9" t="n">
+      <c r="F62" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="21" t="n">
         <v>357</v>
       </c>
-      <c r="H62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" s="9" t="n">
+      <c r="H62" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="21" t="n">
         <v>357</v>
       </c>
       <c r="P62" s="7" t="inlineStr">
@@ -4737,41 +4744,41 @@
           <t>P-2049</t>
         </is>
       </c>
-      <c r="C63" s="8" t="n">
+      <c r="C63" s="20" t="n">
         <v>46165</v>
       </c>
-      <c r="D63" s="8" t="n"/>
-      <c r="E63" s="9" t="n">
+      <c r="D63" s="20" t="n"/>
+      <c r="E63" s="21" t="n">
         <v>3362.32</v>
       </c>
-      <c r="F63" s="9" t="n">
+      <c r="F63" s="21" t="n">
         <v>3362.32</v>
       </c>
-      <c r="G63" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" s="9" t="n">
+      <c r="G63" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="21" t="n">
         <v>3362.32</v>
       </c>
-      <c r="L63" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" s="9" t="n">
+      <c r="L63" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P63" s="7" t="inlineStr">
@@ -4800,41 +4807,41 @@
           <t>P-2050</t>
         </is>
       </c>
-      <c r="C64" s="8" t="n">
+      <c r="C64" s="20" t="n">
         <v>45901</v>
       </c>
-      <c r="D64" s="8" t="n"/>
-      <c r="E64" s="9" t="n">
+      <c r="D64" s="20" t="n"/>
+      <c r="E64" s="21" t="n">
         <v>15.2</v>
       </c>
-      <c r="F64" s="9" t="n">
+      <c r="F64" s="21" t="n">
         <v>15.2</v>
       </c>
-      <c r="G64" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" s="9" t="n">
+      <c r="G64" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="21" t="n">
         <v>15.2</v>
       </c>
-      <c r="L64" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" s="9" t="n">
+      <c r="L64" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P64" s="7" t="inlineStr">
@@ -4863,44 +4870,44 @@
           <t>P-2051</t>
         </is>
       </c>
-      <c r="C65" s="8" t="n">
+      <c r="C65" s="20" t="n">
         <v>45917</v>
       </c>
-      <c r="D65" s="8">
+      <c r="D65" s="20">
         <f>TODAY()+36</f>
         <v/>
       </c>
-      <c r="E65" s="9" t="n">
+      <c r="E65" s="21" t="n">
         <v>116</v>
       </c>
-      <c r="F65" s="9" t="n">
+      <c r="F65" s="21" t="n">
         <v>116</v>
       </c>
-      <c r="G65" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" s="9" t="n">
+      <c r="G65" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" s="21" t="n">
         <v>116</v>
       </c>
-      <c r="L65" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" s="9" t="n">
+      <c r="L65" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P65" s="7" t="inlineStr">
@@ -4929,41 +4936,41 @@
           <t>P-2042</t>
         </is>
       </c>
-      <c r="C66" s="8" t="n">
+      <c r="C66" s="20" t="n">
         <v>46169</v>
       </c>
-      <c r="D66" s="8" t="n"/>
-      <c r="E66" s="9" t="n">
+      <c r="D66" s="20" t="n"/>
+      <c r="E66" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="F66" s="9" t="n">
+      <c r="F66" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="G66" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" s="9" t="n">
+      <c r="G66" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="L66" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" s="9" t="n">
+      <c r="L66" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P66" s="7" t="inlineStr">
@@ -4992,41 +4999,41 @@
           <t>P-2052</t>
         </is>
       </c>
-      <c r="C67" s="8" t="n">
+      <c r="C67" s="20" t="n">
         <v>46029</v>
       </c>
-      <c r="D67" s="8" t="n"/>
-      <c r="E67" s="9" t="n">
+      <c r="D67" s="20" t="n"/>
+      <c r="E67" s="21" t="n">
         <v>21.8</v>
       </c>
-      <c r="F67" s="9" t="n">
+      <c r="F67" s="21" t="n">
         <v>21.8</v>
       </c>
-      <c r="G67" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" s="9" t="n">
+      <c r="G67" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" s="21" t="n">
         <v>21.8</v>
       </c>
-      <c r="L67" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O67" s="9" t="n">
+      <c r="L67" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P67" s="7" t="inlineStr">
@@ -5055,41 +5062,41 @@
           <t>P-2053</t>
         </is>
       </c>
-      <c r="C68" s="8" t="n">
+      <c r="C68" s="20" t="n">
         <v>45907</v>
       </c>
-      <c r="D68" s="8" t="n"/>
-      <c r="E68" s="9" t="n">
+      <c r="D68" s="20" t="n"/>
+      <c r="E68" s="21" t="n">
         <v>88</v>
       </c>
-      <c r="F68" s="9" t="n">
+      <c r="F68" s="21" t="n">
         <v>88</v>
       </c>
-      <c r="G68" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" s="9" t="n">
+      <c r="G68" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" s="21" t="n">
         <v>88</v>
       </c>
-      <c r="L68" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" s="9" t="n">
+      <c r="L68" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P68" s="7" t="inlineStr">
@@ -5118,44 +5125,44 @@
           <t>P-2054</t>
         </is>
       </c>
-      <c r="C69" s="8" t="n">
+      <c r="C69" s="20" t="n">
         <v>45925</v>
       </c>
-      <c r="D69" s="8">
+      <c r="D69" s="20">
         <f>TODAY()+70</f>
         <v/>
       </c>
-      <c r="E69" s="9" t="n">
+      <c r="E69" s="21" t="n">
         <v>50</v>
       </c>
-      <c r="F69" s="9" t="n">
+      <c r="F69" s="21" t="n">
         <v>50</v>
       </c>
-      <c r="G69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" s="9" t="n">
+      <c r="G69" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" s="21" t="n">
         <v>50</v>
       </c>
-      <c r="L69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" s="9" t="n">
+      <c r="L69" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P69" s="7" t="inlineStr">
@@ -5184,44 +5191,44 @@
           <t>P-2055</t>
         </is>
       </c>
-      <c r="C70" s="8" t="n">
+      <c r="C70" s="20" t="n">
         <v>46056</v>
       </c>
-      <c r="D70" s="8">
+      <c r="D70" s="20">
         <f>TODAY()+31</f>
         <v/>
       </c>
-      <c r="E70" s="9" t="n">
+      <c r="E70" s="21" t="n">
         <v>20.8</v>
       </c>
-      <c r="F70" s="9" t="n">
+      <c r="F70" s="21" t="n">
         <v>20.8</v>
       </c>
-      <c r="G70" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" s="9" t="n">
+      <c r="G70" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" s="21" t="n">
         <v>20.8</v>
       </c>
-      <c r="L70" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" s="9" t="n">
+      <c r="L70" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P70" s="7" t="inlineStr">
@@ -5250,41 +5257,41 @@
           <t>P-2056</t>
         </is>
       </c>
-      <c r="C71" s="8" t="n">
+      <c r="C71" s="20" t="n">
         <v>46010</v>
       </c>
-      <c r="D71" s="8" t="n"/>
-      <c r="E71" s="9" t="n">
+      <c r="D71" s="20" t="n"/>
+      <c r="E71" s="21" t="n">
         <v>109</v>
       </c>
-      <c r="F71" s="9" t="n">
+      <c r="F71" s="21" t="n">
         <v>109</v>
       </c>
-      <c r="G71" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" s="9" t="n">
+      <c r="G71" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="21" t="n">
         <v>109</v>
       </c>
-      <c r="L71" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" s="9" t="n">
+      <c r="L71" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P71" s="7" t="inlineStr">
@@ -5313,44 +5320,44 @@
           <t>P-2024</t>
         </is>
       </c>
-      <c r="C72" s="8" t="n">
+      <c r="C72" s="20" t="n">
         <v>46079</v>
       </c>
-      <c r="D72" s="8">
+      <c r="D72" s="20">
         <f>TODAY()+10</f>
         <v/>
       </c>
-      <c r="E72" s="9" t="n">
+      <c r="E72" s="21" t="n">
         <v>311</v>
       </c>
-      <c r="F72" s="9" t="n">
+      <c r="F72" s="21" t="n">
         <v>90</v>
       </c>
-      <c r="G72" s="9" t="n">
+      <c r="G72" s="21" t="n">
         <v>221</v>
       </c>
-      <c r="H72" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" s="9" t="n">
+      <c r="H72" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" s="21" t="n">
         <v>90</v>
       </c>
-      <c r="L72" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N72" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" s="9" t="n">
+      <c r="L72" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="21" t="n">
         <v>221</v>
       </c>
       <c r="P72" s="7" t="inlineStr">
@@ -5379,41 +5386,41 @@
           <t>P-2013</t>
         </is>
       </c>
-      <c r="C73" s="8" t="n">
+      <c r="C73" s="20" t="n">
         <v>46152</v>
       </c>
-      <c r="D73" s="8" t="n"/>
-      <c r="E73" s="9" t="n">
+      <c r="D73" s="20" t="n"/>
+      <c r="E73" s="21" t="n">
         <v>61.2</v>
       </c>
-      <c r="F73" s="9" t="n">
+      <c r="F73" s="21" t="n">
         <v>61.2</v>
       </c>
-      <c r="G73" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" s="9" t="n">
+      <c r="G73" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="21" t="n">
         <v>61.2</v>
       </c>
-      <c r="L73" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O73" s="9" t="n">
+      <c r="L73" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P73" s="7" t="inlineStr">
@@ -5442,41 +5449,41 @@
           <t>P-2057</t>
         </is>
       </c>
-      <c r="C74" s="8" t="n">
+      <c r="C74" s="20" t="n">
         <v>45986</v>
       </c>
-      <c r="D74" s="8" t="n"/>
-      <c r="E74" s="9" t="n">
+      <c r="D74" s="20" t="n"/>
+      <c r="E74" s="21" t="n">
         <v>124.8</v>
       </c>
-      <c r="F74" s="9" t="n">
+      <c r="F74" s="21" t="n">
         <v>124.8</v>
       </c>
-      <c r="G74" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K74" s="9" t="n">
+      <c r="G74" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="21" t="n">
         <v>124.8</v>
       </c>
-      <c r="L74" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N74" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" s="9" t="n">
+      <c r="L74" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P74" s="7" t="inlineStr">
@@ -5505,44 +5512,44 @@
           <t>P-2058</t>
         </is>
       </c>
-      <c r="C75" s="8" t="n">
+      <c r="C75" s="20" t="n">
         <v>45942</v>
       </c>
-      <c r="D75" s="8">
+      <c r="D75" s="20">
         <f>TODAY()+23</f>
         <v/>
       </c>
-      <c r="E75" s="9" t="n">
+      <c r="E75" s="21" t="n">
         <v>208</v>
       </c>
-      <c r="F75" s="9" t="n">
+      <c r="F75" s="21" t="n">
         <v>208</v>
       </c>
-      <c r="G75" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" s="9" t="n">
+      <c r="G75" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" s="21" t="n">
         <v>208</v>
       </c>
-      <c r="L75" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N75" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" s="9" t="n">
+      <c r="L75" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P75" s="7" t="inlineStr">
@@ -5571,44 +5578,44 @@
           <t>P-2059</t>
         </is>
       </c>
-      <c r="C76" s="8" t="n">
+      <c r="C76" s="20" t="n">
         <v>46090</v>
       </c>
-      <c r="D76" s="8">
+      <c r="D76" s="20">
         <f>TODAY()+17</f>
         <v/>
       </c>
-      <c r="E76" s="9" t="n">
+      <c r="E76" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="F76" s="9" t="n">
+      <c r="F76" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="G76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" s="9" t="n">
+      <c r="G76" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="L76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" s="9" t="n">
+      <c r="L76" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P76" s="7" t="inlineStr">
@@ -5637,44 +5644,44 @@
           <t>P-2060</t>
         </is>
       </c>
-      <c r="C77" s="8" t="n">
+      <c r="C77" s="20" t="n">
         <v>45925</v>
       </c>
-      <c r="D77" s="8">
+      <c r="D77" s="20">
         <f>TODAY()+42</f>
         <v/>
       </c>
-      <c r="E77" s="9" t="n">
+      <c r="E77" s="21" t="n">
         <v>3180</v>
       </c>
-      <c r="F77" s="9" t="n">
+      <c r="F77" s="21" t="n">
         <v>3180</v>
       </c>
-      <c r="G77" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" s="9" t="n">
+      <c r="G77" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" s="21" t="n">
         <v>3180</v>
       </c>
-      <c r="L77" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N77" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O77" s="9" t="n">
+      <c r="L77" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P77" s="7" t="inlineStr">
@@ -5703,41 +5710,41 @@
           <t>P-2061</t>
         </is>
       </c>
-      <c r="C78" s="8" t="n">
+      <c r="C78" s="20" t="n">
         <v>46098</v>
       </c>
-      <c r="D78" s="8" t="n"/>
-      <c r="E78" s="9" t="n">
+      <c r="D78" s="20" t="n"/>
+      <c r="E78" s="21" t="n">
         <v>72.40000000000001</v>
       </c>
-      <c r="F78" s="9" t="n">
+      <c r="F78" s="21" t="n">
         <v>72.40000000000001</v>
       </c>
-      <c r="G78" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" s="9" t="n">
+      <c r="G78" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" s="21" t="n">
         <v>72.40000000000001</v>
       </c>
-      <c r="L78" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N78" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" s="9" t="n">
+      <c r="L78" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P78" s="7" t="inlineStr">
@@ -5766,41 +5773,41 @@
           <t>P-2040</t>
         </is>
       </c>
-      <c r="C79" s="8" t="n">
+      <c r="C79" s="20" t="n">
         <v>45901</v>
       </c>
-      <c r="D79" s="8" t="n"/>
-      <c r="E79" s="9" t="n">
+      <c r="D79" s="20" t="n"/>
+      <c r="E79" s="21" t="n">
         <v>17</v>
       </c>
-      <c r="F79" s="9" t="n">
+      <c r="F79" s="21" t="n">
         <v>17</v>
       </c>
-      <c r="G79" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" s="9" t="n">
+      <c r="G79" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" s="21" t="n">
         <v>17</v>
       </c>
-      <c r="L79" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N79" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" s="9" t="n">
+      <c r="L79" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P79" s="7" t="inlineStr">
@@ -5829,41 +5836,41 @@
           <t>P-2062</t>
         </is>
       </c>
-      <c r="C80" s="8" t="n">
+      <c r="C80" s="20" t="n">
         <v>46010</v>
       </c>
-      <c r="D80" s="8" t="n"/>
-      <c r="E80" s="9" t="n">
+      <c r="D80" s="20" t="n"/>
+      <c r="E80" s="21" t="n">
         <v>82</v>
       </c>
-      <c r="F80" s="9" t="n">
+      <c r="F80" s="21" t="n">
         <v>82</v>
       </c>
-      <c r="G80" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" s="9" t="n">
+      <c r="G80" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" s="21" t="n">
         <v>82</v>
       </c>
-      <c r="L80" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" s="9" t="n">
+      <c r="L80" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P80" s="7" t="inlineStr">
@@ -5892,41 +5899,41 @@
           <t>P-2063</t>
         </is>
       </c>
-      <c r="C81" s="8" t="n">
+      <c r="C81" s="20" t="n">
         <v>45938</v>
       </c>
-      <c r="D81" s="8" t="n"/>
-      <c r="E81" s="9" t="n">
+      <c r="D81" s="20" t="n"/>
+      <c r="E81" s="21" t="n">
         <v>50</v>
       </c>
-      <c r="F81" s="9" t="n">
+      <c r="F81" s="21" t="n">
         <v>50</v>
       </c>
-      <c r="G81" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" s="9" t="n">
+      <c r="G81" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" s="21" t="n">
         <v>50</v>
       </c>
-      <c r="L81" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" s="9" t="n">
+      <c r="L81" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P81" s="7" t="inlineStr">
@@ -5955,41 +5962,41 @@
           <t>P-2064</t>
         </is>
       </c>
-      <c r="C82" s="8" t="n">
+      <c r="C82" s="20" t="n">
         <v>45939</v>
       </c>
-      <c r="D82" s="8" t="n"/>
-      <c r="E82" s="9" t="n">
+      <c r="D82" s="20" t="n"/>
+      <c r="E82" s="21" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="F82" s="9" t="n">
+      <c r="F82" s="21" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="G82" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H82" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" s="9" t="n">
+      <c r="G82" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" s="21" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="L82" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" s="9" t="n">
+      <c r="L82" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P82" s="7" t="inlineStr">
@@ -6018,41 +6025,41 @@
           <t>P-2065</t>
         </is>
       </c>
-      <c r="C83" s="8" t="n">
+      <c r="C83" s="20" t="n">
         <v>46058</v>
       </c>
-      <c r="D83" s="8" t="n"/>
-      <c r="E83" s="9" t="n">
+      <c r="D83" s="20" t="n"/>
+      <c r="E83" s="21" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="F83" s="9" t="n">
+      <c r="F83" s="21" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="G83" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" s="9" t="n">
+      <c r="G83" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" s="21" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="L83" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N83" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O83" s="9" t="n">
+      <c r="L83" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P83" s="7" t="inlineStr">
@@ -6081,41 +6088,41 @@
           <t>P-2066</t>
         </is>
       </c>
-      <c r="C84" s="8" t="n">
+      <c r="C84" s="20" t="n">
         <v>45938</v>
       </c>
-      <c r="D84" s="8" t="n"/>
-      <c r="E84" s="9" t="n">
+      <c r="D84" s="20" t="n"/>
+      <c r="E84" s="21" t="n">
         <v>339</v>
       </c>
-      <c r="F84" s="9" t="n">
+      <c r="F84" s="21" t="n">
         <v>339</v>
       </c>
-      <c r="G84" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H84" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" s="9" t="n">
+      <c r="G84" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" s="21" t="n">
         <v>339</v>
       </c>
-      <c r="L84" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N84" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O84" s="9" t="n">
+      <c r="L84" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P84" s="7" t="inlineStr">
@@ -6144,44 +6151,44 @@
           <t>P-2067</t>
         </is>
       </c>
-      <c r="C85" s="8" t="n">
+      <c r="C85" s="20" t="n">
         <v>46005</v>
       </c>
-      <c r="D85" s="8">
+      <c r="D85" s="20">
         <f>TODAY()+37</f>
         <v/>
       </c>
-      <c r="E85" s="9" t="n">
+      <c r="E85" s="21" t="n">
         <v>208</v>
       </c>
-      <c r="F85" s="9" t="n">
+      <c r="F85" s="21" t="n">
         <v>208</v>
       </c>
-      <c r="G85" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H85" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" s="9" t="n">
+      <c r="G85" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="21" t="n">
         <v>208</v>
       </c>
-      <c r="L85" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N85" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O85" s="9" t="n">
+      <c r="L85" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P85" s="7" t="inlineStr">
@@ -6210,41 +6217,41 @@
           <t>P-2068</t>
         </is>
       </c>
-      <c r="C86" s="8" t="n">
+      <c r="C86" s="20" t="n">
         <v>45911</v>
       </c>
-      <c r="D86" s="8" t="n"/>
-      <c r="E86" s="9" t="n">
+      <c r="D86" s="20" t="n"/>
+      <c r="E86" s="21" t="n">
         <v>21.2</v>
       </c>
-      <c r="F86" s="9" t="n">
+      <c r="F86" s="21" t="n">
         <v>21.2</v>
       </c>
-      <c r="G86" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H86" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" s="9" t="n">
+      <c r="G86" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="21" t="n">
         <v>21.2</v>
       </c>
-      <c r="L86" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N86" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O86" s="9" t="n">
+      <c r="L86" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P86" s="7" t="inlineStr">
@@ -6273,44 +6280,44 @@
           <t>P-2069</t>
         </is>
       </c>
-      <c r="C87" s="8" t="n">
+      <c r="C87" s="20" t="n">
         <v>45896</v>
       </c>
-      <c r="D87" s="8">
+      <c r="D87" s="20">
         <f>TODAY()+10</f>
         <v/>
       </c>
-      <c r="E87" s="9" t="n">
+      <c r="E87" s="21" t="n">
         <v>10.5</v>
       </c>
-      <c r="F87" s="9" t="n">
+      <c r="F87" s="21" t="n">
         <v>10.5</v>
       </c>
-      <c r="G87" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H87" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" s="9" t="n">
+      <c r="G87" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="21" t="n">
         <v>10.5</v>
       </c>
-      <c r="L87" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N87" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O87" s="9" t="n">
+      <c r="L87" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P87" s="7" t="inlineStr">
@@ -6339,41 +6346,41 @@
           <t>P-2070</t>
         </is>
       </c>
-      <c r="C88" s="8" t="n">
+      <c r="C88" s="20" t="n">
         <v>45942</v>
       </c>
-      <c r="D88" s="8" t="n"/>
-      <c r="E88" s="9" t="n">
+      <c r="D88" s="20" t="n"/>
+      <c r="E88" s="21" t="n">
         <v>54</v>
       </c>
-      <c r="F88" s="9" t="n">
+      <c r="F88" s="21" t="n">
         <v>54</v>
       </c>
-      <c r="G88" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H88" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" s="9" t="n">
+      <c r="G88" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" s="21" t="n">
         <v>54</v>
       </c>
-      <c r="L88" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O88" s="9" t="n">
+      <c r="L88" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P88" s="7" t="inlineStr">
@@ -6402,41 +6409,41 @@
           <t>P-2071</t>
         </is>
       </c>
-      <c r="C89" s="8" t="n">
+      <c r="C89" s="20" t="n">
         <v>46046</v>
       </c>
-      <c r="D89" s="8" t="n"/>
-      <c r="E89" s="9" t="n">
+      <c r="D89" s="20" t="n"/>
+      <c r="E89" s="21" t="n">
         <v>22</v>
       </c>
-      <c r="F89" s="9" t="n">
+      <c r="F89" s="21" t="n">
         <v>22</v>
       </c>
-      <c r="G89" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H89" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" s="9" t="n">
+      <c r="G89" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" s="21" t="n">
         <v>22</v>
       </c>
-      <c r="L89" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N89" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O89" s="9" t="n">
+      <c r="L89" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P89" s="7" t="inlineStr">
@@ -6465,41 +6472,41 @@
           <t>P-2072</t>
         </is>
       </c>
-      <c r="C90" s="8" t="n">
+      <c r="C90" s="20" t="n">
         <v>46000</v>
       </c>
-      <c r="D90" s="8" t="n"/>
-      <c r="E90" s="9" t="n">
+      <c r="D90" s="20" t="n"/>
+      <c r="E90" s="21" t="n">
         <v>9.6</v>
       </c>
-      <c r="F90" s="9" t="n">
+      <c r="F90" s="21" t="n">
         <v>9.6</v>
       </c>
-      <c r="G90" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H90" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" s="9" t="n">
+      <c r="G90" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="21" t="n">
         <v>9.6</v>
       </c>
-      <c r="L90" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" s="9" t="n">
+      <c r="L90" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P90" s="7" t="inlineStr">
@@ -6528,44 +6535,44 @@
           <t>P-2073</t>
         </is>
       </c>
-      <c r="C91" s="8" t="n">
+      <c r="C91" s="20" t="n">
         <v>46074</v>
       </c>
-      <c r="D91" s="8">
+      <c r="D91" s="20">
         <f>TODAY()+28</f>
         <v/>
       </c>
-      <c r="E91" s="9" t="n">
+      <c r="E91" s="21" t="n">
         <v>21.2</v>
       </c>
-      <c r="F91" s="9" t="n">
+      <c r="F91" s="21" t="n">
         <v>21.2</v>
       </c>
-      <c r="G91" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H91" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" s="9" t="n">
+      <c r="G91" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" s="21" t="n">
         <v>21.2</v>
       </c>
-      <c r="L91" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" s="9" t="n">
+      <c r="L91" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P91" s="7" t="inlineStr">
@@ -6594,41 +6601,41 @@
           <t>P-2074</t>
         </is>
       </c>
-      <c r="C92" s="8" t="n">
+      <c r="C92" s="20" t="n">
         <v>46127</v>
       </c>
-      <c r="D92" s="8" t="n"/>
-      <c r="E92" s="9" t="n">
+      <c r="D92" s="20" t="n"/>
+      <c r="E92" s="21" t="n">
         <v>50</v>
       </c>
-      <c r="F92" s="9" t="n">
+      <c r="F92" s="21" t="n">
         <v>50</v>
       </c>
-      <c r="G92" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" s="9" t="n">
+      <c r="G92" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" s="21" t="n">
         <v>50</v>
       </c>
-      <c r="L92" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M92" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N92" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O92" s="9" t="n">
+      <c r="L92" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P92" s="7" t="inlineStr">
@@ -6657,44 +6664,44 @@
           <t>P-2075</t>
         </is>
       </c>
-      <c r="C93" s="8" t="n">
+      <c r="C93" s="20" t="n">
         <v>45899</v>
       </c>
-      <c r="D93" s="8">
+      <c r="D93" s="20">
         <f>TODAY()+41</f>
         <v/>
       </c>
-      <c r="E93" s="9" t="n">
+      <c r="E93" s="21" t="n">
         <v>117</v>
       </c>
-      <c r="F93" s="9" t="n">
+      <c r="F93" s="21" t="n">
         <v>117</v>
       </c>
-      <c r="G93" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H93" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J93" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K93" s="9" t="n">
+      <c r="G93" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" s="21" t="n">
         <v>117</v>
       </c>
-      <c r="L93" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M93" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N93" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O93" s="9" t="n">
+      <c r="L93" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P93" s="7" t="inlineStr">
@@ -6723,44 +6730,44 @@
           <t>P-2076</t>
         </is>
       </c>
-      <c r="C94" s="8" t="n">
+      <c r="C94" s="20" t="n">
         <v>46076</v>
       </c>
-      <c r="D94" s="8">
+      <c r="D94" s="20">
         <f>TODAY()+14</f>
         <v/>
       </c>
-      <c r="E94" s="9" t="n">
+      <c r="E94" s="21" t="n">
         <v>28.6</v>
       </c>
-      <c r="F94" s="9" t="n">
+      <c r="F94" s="21" t="n">
         <v>28.6</v>
       </c>
-      <c r="G94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K94" s="9" t="n">
+      <c r="G94" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" s="21" t="n">
         <v>28.6</v>
       </c>
-      <c r="L94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O94" s="9" t="n">
+      <c r="L94" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P94" s="7" t="inlineStr">
@@ -6789,41 +6796,41 @@
           <t>P-2077</t>
         </is>
       </c>
-      <c r="C95" s="8" t="n">
+      <c r="C95" s="20" t="n">
         <v>45997</v>
       </c>
-      <c r="D95" s="8" t="n"/>
-      <c r="E95" s="9" t="n">
+      <c r="D95" s="20" t="n"/>
+      <c r="E95" s="21" t="n">
         <v>14.2</v>
       </c>
-      <c r="F95" s="9" t="n">
+      <c r="F95" s="21" t="n">
         <v>14.2</v>
       </c>
-      <c r="G95" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K95" s="9" t="n">
+      <c r="G95" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" s="21" t="n">
         <v>14.2</v>
       </c>
-      <c r="L95" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M95" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N95" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" s="9" t="n">
+      <c r="L95" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P95" s="7" t="inlineStr">
@@ -6852,41 +6859,41 @@
           <t>P-2078</t>
         </is>
       </c>
-      <c r="C96" s="8" t="n">
+      <c r="C96" s="20" t="n">
         <v>46075</v>
       </c>
-      <c r="D96" s="8" t="n"/>
-      <c r="E96" s="9" t="n">
+      <c r="D96" s="20" t="n"/>
+      <c r="E96" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="F96" s="9" t="n">
+      <c r="F96" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="G96" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" s="9" t="n">
+      <c r="G96" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="L96" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M96" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N96" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" s="9" t="n">
+      <c r="L96" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P96" s="7" t="inlineStr">
@@ -6915,41 +6922,41 @@
           <t>P-2029</t>
         </is>
       </c>
-      <c r="C97" s="8" t="n">
+      <c r="C97" s="20" t="n">
         <v>46067</v>
       </c>
-      <c r="D97" s="8" t="n"/>
-      <c r="E97" s="9" t="n">
+      <c r="D97" s="20" t="n"/>
+      <c r="E97" s="21" t="n">
         <v>311</v>
       </c>
-      <c r="F97" s="9" t="n">
+      <c r="F97" s="21" t="n">
         <v>311</v>
       </c>
-      <c r="G97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" s="9" t="n">
+      <c r="G97" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" s="21" t="n">
         <v>311</v>
       </c>
-      <c r="L97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O97" s="9" t="n">
+      <c r="L97" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P97" s="7" t="inlineStr">
@@ -6978,41 +6985,41 @@
           <t>P-2079</t>
         </is>
       </c>
-      <c r="C98" s="8" t="n">
+      <c r="C98" s="20" t="n">
         <v>45919</v>
       </c>
-      <c r="D98" s="8" t="n"/>
-      <c r="E98" s="9" t="n">
+      <c r="D98" s="20" t="n"/>
+      <c r="E98" s="21" t="n">
         <v>16</v>
       </c>
-      <c r="F98" s="9" t="n">
+      <c r="F98" s="21" t="n">
         <v>16</v>
       </c>
-      <c r="G98" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J98" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K98" s="9" t="n">
+      <c r="G98" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" s="21" t="n">
         <v>16</v>
       </c>
-      <c r="L98" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M98" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N98" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O98" s="9" t="n">
+      <c r="L98" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P98" s="7" t="inlineStr">
@@ -7041,41 +7048,41 @@
           <t>P-2049</t>
         </is>
       </c>
-      <c r="C99" s="8" t="n">
+      <c r="C99" s="20" t="n">
         <v>46165</v>
       </c>
-      <c r="D99" s="8" t="n"/>
-      <c r="E99" s="9" t="n">
+      <c r="D99" s="20" t="n"/>
+      <c r="E99" s="21" t="n">
         <v>396</v>
       </c>
-      <c r="F99" s="9" t="n">
+      <c r="F99" s="21" t="n">
         <v>298</v>
       </c>
-      <c r="G99" s="9" t="n">
+      <c r="G99" s="21" t="n">
         <v>98</v>
       </c>
-      <c r="H99" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K99" s="9" t="n">
+      <c r="H99" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" s="21" t="n">
         <v>298</v>
       </c>
-      <c r="L99" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O99" s="9" t="n">
+      <c r="L99" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="21" t="n">
         <v>98</v>
       </c>
       <c r="P99" s="7" t="inlineStr">
@@ -7104,41 +7111,41 @@
           <t>P-2080</t>
         </is>
       </c>
-      <c r="C100" s="8" t="n">
+      <c r="C100" s="20" t="n">
         <v>45960</v>
       </c>
-      <c r="D100" s="8" t="n"/>
-      <c r="E100" s="9" t="n">
+      <c r="D100" s="20" t="n"/>
+      <c r="E100" s="21" t="n">
         <v>42</v>
       </c>
-      <c r="F100" s="9" t="n">
+      <c r="F100" s="21" t="n">
         <v>42</v>
       </c>
-      <c r="G100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" s="9" t="n">
+      <c r="G100" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" s="21" t="n">
         <v>42</v>
       </c>
-      <c r="L100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O100" s="9" t="n">
+      <c r="L100" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P100" s="7" t="inlineStr">
@@ -7167,44 +7174,44 @@
           <t>P-2081</t>
         </is>
       </c>
-      <c r="C101" s="8" t="n">
+      <c r="C101" s="20" t="n">
         <v>46173</v>
       </c>
-      <c r="D101" s="8">
+      <c r="D101" s="20">
         <f>TODAY()+64</f>
         <v/>
       </c>
-      <c r="E101" s="9" t="n">
+      <c r="E101" s="21" t="n">
         <v>59.6</v>
       </c>
-      <c r="F101" s="9" t="n">
+      <c r="F101" s="21" t="n">
         <v>59.6</v>
       </c>
-      <c r="G101" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J101" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K101" s="9" t="n">
+      <c r="G101" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" s="21" t="n">
         <v>59.6</v>
       </c>
-      <c r="L101" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O101" s="9" t="n">
+      <c r="L101" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P101" s="7" t="inlineStr">
@@ -7233,44 +7240,44 @@
           <t>P-2082</t>
         </is>
       </c>
-      <c r="C102" s="8" t="n">
+      <c r="C102" s="20" t="n">
         <v>45934</v>
       </c>
-      <c r="D102" s="8">
+      <c r="D102" s="20">
         <f>TODAY()+59</f>
         <v/>
       </c>
-      <c r="E102" s="9" t="n">
+      <c r="E102" s="21" t="n">
         <v>1549</v>
       </c>
-      <c r="F102" s="9" t="n">
+      <c r="F102" s="21" t="n">
         <v>1048</v>
       </c>
-      <c r="G102" s="9" t="n">
+      <c r="G102" s="21" t="n">
         <v>501</v>
       </c>
-      <c r="H102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" s="9" t="n">
+      <c r="H102" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" s="21" t="n">
         <v>1048</v>
       </c>
-      <c r="L102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O102" s="9" t="n">
+      <c r="L102" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" s="21" t="n">
         <v>501</v>
       </c>
       <c r="P102" s="7" t="inlineStr">
@@ -7299,41 +7306,41 @@
           <t>P-2083</t>
         </is>
       </c>
-      <c r="C103" s="8" t="n">
+      <c r="C103" s="20" t="n">
         <v>46057</v>
       </c>
-      <c r="D103" s="8" t="n"/>
-      <c r="E103" s="9" t="n">
+      <c r="D103" s="20" t="n"/>
+      <c r="E103" s="21" t="n">
         <v>1127</v>
       </c>
-      <c r="F103" s="9" t="n">
+      <c r="F103" s="21" t="n">
         <v>773</v>
       </c>
-      <c r="G103" s="9" t="n">
+      <c r="G103" s="21" t="n">
         <v>354</v>
       </c>
-      <c r="H103" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I103" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J103" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K103" s="9" t="n">
+      <c r="H103" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" s="21" t="n">
         <v>773</v>
       </c>
-      <c r="L103" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M103" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N103" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O103" s="9" t="n">
+      <c r="L103" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" s="21" t="n">
         <v>354</v>
       </c>
       <c r="P103" s="7" t="inlineStr">
@@ -7362,41 +7369,41 @@
           <t>P-2016</t>
         </is>
       </c>
-      <c r="C104" s="8" t="n">
+      <c r="C104" s="20" t="n">
         <v>45984</v>
       </c>
-      <c r="D104" s="8" t="n"/>
-      <c r="E104" s="9" t="n">
+      <c r="D104" s="20" t="n"/>
+      <c r="E104" s="21" t="n">
         <v>59.6</v>
       </c>
-      <c r="F104" s="9" t="n">
+      <c r="F104" s="21" t="n">
         <v>59.6</v>
       </c>
-      <c r="G104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K104" s="9" t="n">
+      <c r="G104" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" s="21" t="n">
         <v>59.6</v>
       </c>
-      <c r="L104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O104" s="9" t="n">
+      <c r="L104" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P104" s="7" t="inlineStr">
@@ -7425,44 +7432,44 @@
           <t>P-2084</t>
         </is>
       </c>
-      <c r="C105" s="8" t="n">
+      <c r="C105" s="20" t="n">
         <v>45933</v>
       </c>
-      <c r="D105" s="8">
+      <c r="D105" s="20">
         <f>TODAY()+66</f>
         <v/>
       </c>
-      <c r="E105" s="9" t="n">
+      <c r="E105" s="21" t="n">
         <v>49.8</v>
       </c>
-      <c r="F105" s="9" t="n">
+      <c r="F105" s="21" t="n">
         <v>49.8</v>
       </c>
-      <c r="G105" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H105" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I105" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J105" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K105" s="9" t="n">
+      <c r="G105" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" s="21" t="n">
         <v>49.8</v>
       </c>
-      <c r="L105" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M105" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N105" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O105" s="9" t="n">
+      <c r="L105" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P105" s="7" t="inlineStr">
@@ -7491,44 +7498,44 @@
           <t>P-2085</t>
         </is>
       </c>
-      <c r="C106" s="8" t="n">
+      <c r="C106" s="20" t="n">
         <v>46071</v>
       </c>
-      <c r="D106" s="8">
+      <c r="D106" s="20">
         <f>TODAY()+47</f>
         <v/>
       </c>
-      <c r="E106" s="9" t="n">
+      <c r="E106" s="21" t="n">
         <v>21.8</v>
       </c>
-      <c r="F106" s="9" t="n">
+      <c r="F106" s="21" t="n">
         <v>21.8</v>
       </c>
-      <c r="G106" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H106" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I106" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" s="9" t="n">
+      <c r="G106" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" s="21" t="n">
         <v>21.8</v>
       </c>
-      <c r="L106" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M106" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N106" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O106" s="9" t="n">
+      <c r="L106" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P106" s="7" t="inlineStr">
@@ -7557,41 +7564,41 @@
           <t>P-2086</t>
         </is>
       </c>
-      <c r="C107" s="8" t="n">
+      <c r="C107" s="20" t="n">
         <v>46069</v>
       </c>
-      <c r="D107" s="8" t="n"/>
-      <c r="E107" s="9" t="n">
+      <c r="D107" s="20" t="n"/>
+      <c r="E107" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="F107" s="9" t="n">
+      <c r="F107" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="G107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K107" s="9" t="n">
+      <c r="G107" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="L107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O107" s="9" t="n">
+      <c r="L107" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P107" s="7" t="inlineStr">
@@ -7620,44 +7627,44 @@
           <t>P-2087</t>
         </is>
       </c>
-      <c r="C108" s="8" t="n">
+      <c r="C108" s="20" t="n">
         <v>46136</v>
       </c>
-      <c r="D108" s="8">
+      <c r="D108" s="20">
         <f>TODAY()+63</f>
         <v/>
       </c>
-      <c r="E108" s="9" t="n">
+      <c r="E108" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="F108" s="9" t="n">
+      <c r="F108" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="G108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K108" s="9" t="n">
+      <c r="G108" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="L108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O108" s="9" t="n">
+      <c r="L108" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P108" s="7" t="inlineStr">
@@ -7686,44 +7693,44 @@
           <t>P-2088</t>
         </is>
       </c>
-      <c r="C109" s="8" t="n">
+      <c r="C109" s="20" t="n">
         <v>46080</v>
       </c>
-      <c r="D109" s="8">
+      <c r="D109" s="20">
         <f>TODAY()+15</f>
         <v/>
       </c>
-      <c r="E109" s="9" t="n">
+      <c r="E109" s="21" t="n">
         <v>51</v>
       </c>
-      <c r="F109" s="9" t="n">
+      <c r="F109" s="21" t="n">
         <v>51</v>
       </c>
-      <c r="G109" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H109" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I109" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J109" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K109" s="9" t="n">
+      <c r="G109" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" s="21" t="n">
         <v>51</v>
       </c>
-      <c r="L109" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M109" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N109" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O109" s="9" t="n">
+      <c r="L109" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P109" s="7" t="inlineStr">
@@ -7752,44 +7759,44 @@
           <t>P-2089</t>
         </is>
       </c>
-      <c r="C110" s="8" t="n">
+      <c r="C110" s="20" t="n">
         <v>46174</v>
       </c>
-      <c r="D110" s="8">
+      <c r="D110" s="20">
         <f>TODAY()+11</f>
         <v/>
       </c>
-      <c r="E110" s="9" t="n">
+      <c r="E110" s="21" t="n">
         <v>69</v>
       </c>
-      <c r="F110" s="9" t="n">
+      <c r="F110" s="21" t="n">
         <v>69</v>
       </c>
-      <c r="G110" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H110" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I110" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J110" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K110" s="9" t="n">
+      <c r="G110" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" s="21" t="n">
         <v>69</v>
       </c>
-      <c r="L110" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M110" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N110" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O110" s="9" t="n">
+      <c r="L110" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P110" s="7" t="inlineStr">
@@ -7818,44 +7825,44 @@
           <t>P-2090</t>
         </is>
       </c>
-      <c r="C111" s="8" t="n">
+      <c r="C111" s="20" t="n">
         <v>45994</v>
       </c>
-      <c r="D111" s="8">
+      <c r="D111" s="20">
         <f>TODAY()+13</f>
         <v/>
       </c>
-      <c r="E111" s="9" t="n">
+      <c r="E111" s="21" t="n">
         <v>27.5</v>
       </c>
-      <c r="F111" s="9" t="n">
+      <c r="F111" s="21" t="n">
         <v>27.5</v>
       </c>
-      <c r="G111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K111" s="9" t="n">
+      <c r="G111" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" s="21" t="n">
         <v>27.5</v>
       </c>
-      <c r="L111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O111" s="9" t="n">
+      <c r="L111" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" s="21" t="n">
         <v>0</v>
       </c>
       <c r="P111" s="7" t="inlineStr">
@@ -7911,6 +7918,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
@@ -7935,7 +7943,7 @@
           <t>Total owing</t>
         </is>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="22">
         <f>SUM(Ledger!E2:E111)</f>
         <v/>
       </c>
@@ -7946,7 +7954,7 @@
           <t>Patient owing</t>
         </is>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="22">
         <f>SUM(Ledger!F2:F111)</f>
         <v/>
       </c>
@@ -7957,7 +7965,7 @@
           <t>Insurance owing</t>
         </is>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="22">
         <f>SUM(Ledger!G2:G111)</f>
         <v/>
       </c>
@@ -7968,7 +7976,7 @@
           <t>Patient share of open</t>
         </is>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="23">
         <f>IF(B5=0,0,B6/B5)</f>
         <v/>
       </c>
@@ -7979,7 +7987,7 @@
           <t>Patient over 90</t>
         </is>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="22">
         <f>SUM(Ledger!K2:K111)</f>
         <v/>
       </c>
@@ -7990,7 +7998,7 @@
           <t>90+ share of patient $</t>
         </is>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="23">
         <f>IF(B6=0,0,B9/B6)</f>
         <v/>
       </c>
@@ -8028,6 +8036,7 @@
         <v/>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
@@ -8068,19 +8077,19 @@
           <t>0–30</t>
         </is>
       </c>
-      <c r="B17" s="14">
+      <c r="B17" s="22">
         <f>SUM(Ledger!H2:H111)</f>
         <v/>
       </c>
-      <c r="C17" s="14">
+      <c r="C17" s="22">
         <f>SUM(Ledger!L2:L111)</f>
         <v/>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="22">
         <f>B17+C17</f>
         <v/>
       </c>
-      <c r="E17" s="15">
+      <c r="E17" s="23">
         <f>IF($D$21=0,0,D17/$D$21)</f>
         <v/>
       </c>
@@ -8091,19 +8100,19 @@
           <t>31–60</t>
         </is>
       </c>
-      <c r="B18" s="14">
+      <c r="B18" s="22">
         <f>SUM(Ledger!I2:I111)</f>
         <v/>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="22">
         <f>SUM(Ledger!M2:M111)</f>
         <v/>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="22">
         <f>B18+C18</f>
         <v/>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="23">
         <f>IF($D$21=0,0,D18/$D$21)</f>
         <v/>
       </c>
@@ -8114,19 +8123,19 @@
           <t>61–90</t>
         </is>
       </c>
-      <c r="B19" s="14">
+      <c r="B19" s="22">
         <f>SUM(Ledger!J2:J111)</f>
         <v/>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="22">
         <f>SUM(Ledger!N2:N111)</f>
         <v/>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="22">
         <f>B19+C19</f>
         <v/>
       </c>
-      <c r="E19" s="15">
+      <c r="E19" s="23">
         <f>IF($D$21=0,0,D19/$D$21)</f>
         <v/>
       </c>
@@ -8137,19 +8146,19 @@
           <t>90+</t>
         </is>
       </c>
-      <c r="B20" s="14">
+      <c r="B20" s="22">
         <f>SUM(Ledger!K2:K111)</f>
         <v/>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="22">
         <f>SUM(Ledger!O2:O111)</f>
         <v/>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="22">
         <f>B20+C20</f>
         <v/>
       </c>
-      <c r="E20" s="15">
+      <c r="E20" s="23">
         <f>IF($D$21=0,0,D20/$D$21)</f>
         <v/>
       </c>
@@ -8160,27 +8169,28 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B21" s="17">
+      <c r="B21" s="24">
         <f>SUM(B17:B20)</f>
         <v/>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="24">
         <f>SUM(C17:C20)</f>
         <v/>
       </c>
-      <c r="D21" s="17">
+      <c r="D21" s="24">
         <f>SUM(D17:D20)</f>
         <v/>
       </c>
-      <c r="E21" s="18">
+      <c r="E21" s="25">
         <f>SUM(E17:E20)</f>
         <v/>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>Huddle flags</t>
+          <t>Follow-up flags</t>
         </is>
       </c>
     </row>
@@ -8201,7 +8211,7 @@
           <t>Open $ on those accounts</t>
         </is>
       </c>
-      <c r="B25" s="14">
+      <c r="B25" s="22">
         <f>SUMIFS(Ledger!E2:E111,Ledger!K2:K111,"&gt;0",Ledger!Q2:Q111,"No")</f>
         <v/>
       </c>
@@ -8245,6 +8255,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -8278,11 +8289,11 @@
           <t>0–30</t>
         </is>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="22">
         <f>SUMIF(Ledger!P:P,A5,Ledger!F:F)</f>
         <v/>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="22">
         <f>SUMIF(Ledger!P:P,A5,Ledger!G:G)</f>
         <v/>
       </c>
@@ -8301,11 +8312,11 @@
           <t>31–60</t>
         </is>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="22">
         <f>SUMIF(Ledger!P:P,A6,Ledger!F:F)</f>
         <v/>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="22">
         <f>SUMIF(Ledger!P:P,A6,Ledger!G:G)</f>
         <v/>
       </c>
@@ -8324,11 +8335,11 @@
           <t>61–90</t>
         </is>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="22">
         <f>SUMIF(Ledger!P:P,A7,Ledger!F:F)</f>
         <v/>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="22">
         <f>SUMIF(Ledger!P:P,A7,Ledger!G:G)</f>
         <v/>
       </c>
@@ -8347,11 +8358,11 @@
           <t>90+</t>
         </is>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="22">
         <f>SUMIF(Ledger!P:P,A8,Ledger!F:F)</f>
         <v/>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="22">
         <f>SUMIF(Ledger!P:P,A8,Ledger!G:G)</f>
         <v/>
       </c>
@@ -8370,11 +8381,11 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="24">
         <f>SUM(B5:B8)</f>
         <v/>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="24">
         <f>SUM(C5:C8)</f>
         <v/>
       </c>
@@ -8387,6 +8398,7 @@
         <v/>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
@@ -8429,15 +8441,15 @@
           <t>RP-1030</t>
         </is>
       </c>
-      <c r="B14" s="14">
+      <c r="B14" s="22">
         <f>SUMIF(Ledger!A:A,A14,Ledger!E:E)</f>
         <v/>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="22">
         <f>SUMIF(Ledger!A:A,A14,Ledger!F:F)</f>
         <v/>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="22">
         <f>SUMIF(Ledger!A:A,A14,Ledger!G:G)</f>
         <v/>
       </c>
@@ -8448,15 +8460,15 @@
           <t>RP-1038</t>
         </is>
       </c>
-      <c r="B15" s="14">
+      <c r="B15" s="22">
         <f>SUMIF(Ledger!A:A,A15,Ledger!E:E)</f>
         <v/>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="22">
         <f>SUMIF(Ledger!A:A,A15,Ledger!F:F)</f>
         <v/>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="22">
         <f>SUMIF(Ledger!A:A,A15,Ledger!G:G)</f>
         <v/>
       </c>
@@ -8467,15 +8479,15 @@
           <t>RP-1055</t>
         </is>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="22">
         <f>SUMIF(Ledger!A:A,A16,Ledger!E:E)</f>
         <v/>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="22">
         <f>SUMIF(Ledger!A:A,A16,Ledger!F:F)</f>
         <v/>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="22">
         <f>SUMIF(Ledger!A:A,A16,Ledger!G:G)</f>
         <v/>
       </c>
@@ -8486,15 +8498,15 @@
           <t>RP-1019</t>
         </is>
       </c>
-      <c r="B17" s="14">
+      <c r="B17" s="22">
         <f>SUMIF(Ledger!A:A,A17,Ledger!E:E)</f>
         <v/>
       </c>
-      <c r="C17" s="14">
+      <c r="C17" s="22">
         <f>SUMIF(Ledger!A:A,A17,Ledger!F:F)</f>
         <v/>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="22">
         <f>SUMIF(Ledger!A:A,A17,Ledger!G:G)</f>
         <v/>
       </c>
@@ -8505,15 +8517,15 @@
           <t>RP-1015</t>
         </is>
       </c>
-      <c r="B18" s="14">
+      <c r="B18" s="22">
         <f>SUMIF(Ledger!A:A,A18,Ledger!E:E)</f>
         <v/>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="22">
         <f>SUMIF(Ledger!A:A,A18,Ledger!F:F)</f>
         <v/>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="22">
         <f>SUMIF(Ledger!A:A,A18,Ledger!G:G)</f>
         <v/>
       </c>
@@ -8524,15 +8536,15 @@
           <t>RP-1023</t>
         </is>
       </c>
-      <c r="B19" s="14">
+      <c r="B19" s="22">
         <f>SUMIF(Ledger!A:A,A19,Ledger!E:E)</f>
         <v/>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="22">
         <f>SUMIF(Ledger!A:A,A19,Ledger!F:F)</f>
         <v/>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="22">
         <f>SUMIF(Ledger!A:A,A19,Ledger!G:G)</f>
         <v/>
       </c>
@@ -8543,15 +8555,15 @@
           <t>RP-1027</t>
         </is>
       </c>
-      <c r="B20" s="14">
+      <c r="B20" s="22">
         <f>SUMIF(Ledger!A:A,A20,Ledger!E:E)</f>
         <v/>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="22">
         <f>SUMIF(Ledger!A:A,A20,Ledger!F:F)</f>
         <v/>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="22">
         <f>SUMIF(Ledger!A:A,A20,Ledger!G:G)</f>
         <v/>
       </c>
@@ -8562,15 +8574,15 @@
           <t>RP-1005</t>
         </is>
       </c>
-      <c r="B21" s="14">
+      <c r="B21" s="22">
         <f>SUMIF(Ledger!A:A,A21,Ledger!E:E)</f>
         <v/>
       </c>
-      <c r="C21" s="14">
+      <c r="C21" s="22">
         <f>SUMIF(Ledger!A:A,A21,Ledger!F:F)</f>
         <v/>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="22">
         <f>SUMIF(Ledger!A:A,A21,Ledger!G:G)</f>
         <v/>
       </c>
@@ -8581,15 +8593,15 @@
           <t>RP-1009</t>
         </is>
       </c>
-      <c r="B22" s="14">
+      <c r="B22" s="22">
         <f>SUMIF(Ledger!A:A,A22,Ledger!E:E)</f>
         <v/>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="22">
         <f>SUMIF(Ledger!A:A,A22,Ledger!F:F)</f>
         <v/>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="22">
         <f>SUMIF(Ledger!A:A,A22,Ledger!G:G)</f>
         <v/>
       </c>
@@ -8600,15 +8612,15 @@
           <t>RP-1017</t>
         </is>
       </c>
-      <c r="B23" s="14">
+      <c r="B23" s="22">
         <f>SUMIF(Ledger!A:A,A23,Ledger!E:E)</f>
         <v/>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="22">
         <f>SUMIF(Ledger!A:A,A23,Ledger!F:F)</f>
         <v/>
       </c>
-      <c r="D23" s="14">
+      <c r="D23" s="22">
         <f>SUMIF(Ledger!A:A,A23,Ledger!G:G)</f>
         <v/>
       </c>
@@ -8619,15 +8631,15 @@
           <t>RP-1007</t>
         </is>
       </c>
-      <c r="B24" s="14">
+      <c r="B24" s="22">
         <f>SUMIF(Ledger!A:A,A24,Ledger!E:E)</f>
         <v/>
       </c>
-      <c r="C24" s="14">
+      <c r="C24" s="22">
         <f>SUMIF(Ledger!A:A,A24,Ledger!F:F)</f>
         <v/>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="22">
         <f>SUMIF(Ledger!A:A,A24,Ledger!G:G)</f>
         <v/>
       </c>
@@ -8638,15 +8650,15 @@
           <t>RP-1043</t>
         </is>
       </c>
-      <c r="B25" s="14">
+      <c r="B25" s="22">
         <f>SUMIF(Ledger!A:A,A25,Ledger!E:E)</f>
         <v/>
       </c>
-      <c r="C25" s="14">
+      <c r="C25" s="22">
         <f>SUMIF(Ledger!A:A,A25,Ledger!F:F)</f>
         <v/>
       </c>
-      <c r="D25" s="14">
+      <c r="D25" s="22">
         <f>SUMIF(Ledger!A:A,A25,Ledger!G:G)</f>
         <v/>
       </c>
@@ -8657,15 +8669,15 @@
           <t>RP-1036</t>
         </is>
       </c>
-      <c r="B26" s="14">
+      <c r="B26" s="22">
         <f>SUMIF(Ledger!A:A,A26,Ledger!E:E)</f>
         <v/>
       </c>
-      <c r="C26" s="14">
+      <c r="C26" s="22">
         <f>SUMIF(Ledger!A:A,A26,Ledger!F:F)</f>
         <v/>
       </c>
-      <c r="D26" s="14">
+      <c r="D26" s="22">
         <f>SUMIF(Ledger!A:A,A26,Ledger!G:G)</f>
         <v/>
       </c>
@@ -8676,15 +8688,15 @@
           <t>RP-1026</t>
         </is>
       </c>
-      <c r="B27" s="14">
+      <c r="B27" s="22">
         <f>SUMIF(Ledger!A:A,A27,Ledger!E:E)</f>
         <v/>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="22">
         <f>SUMIF(Ledger!A:A,A27,Ledger!F:F)</f>
         <v/>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="22">
         <f>SUMIF(Ledger!A:A,A27,Ledger!G:G)</f>
         <v/>
       </c>
@@ -8695,19 +8707,20 @@
           <t>RP-1012</t>
         </is>
       </c>
-      <c r="B28" s="14">
+      <c r="B28" s="22">
         <f>SUMIF(Ledger!A:A,A28,Ledger!E:E)</f>
         <v/>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="22">
         <f>SUMIF(Ledger!A:A,A28,Ledger!F:F)</f>
         <v/>
       </c>
-      <c r="D28" s="14">
+      <c r="D28" s="22">
         <f>SUMIF(Ledger!A:A,A28,Ledger!G:G)</f>
         <v/>
       </c>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
@@ -8747,11 +8760,11 @@
         <f>COUNTIF(Ledger!Q2:Q111,"Yes")</f>
         <v/>
       </c>
-      <c r="C32" s="14">
+      <c r="C32" s="22">
         <f>SUMIF(Ledger!Q2:Q111,"Yes",Ledger!E2:E111)</f>
         <v/>
       </c>
-      <c r="D32" s="15">
+      <c r="D32" s="23">
         <f>IF($B$34=0,0,B32/$B$34)</f>
         <v/>
       </c>
@@ -8766,11 +8779,11 @@
         <f>COUNTIF(Ledger!Q2:Q111,"No")</f>
         <v/>
       </c>
-      <c r="C33" s="14">
+      <c r="C33" s="22">
         <f>SUMIF(Ledger!Q2:Q111,"No",Ledger!E2:E111)</f>
         <v/>
       </c>
-      <c r="D33" s="15">
+      <c r="D33" s="23">
         <f>IF($B$34=0,0,B33/$B$34)</f>
         <v/>
       </c>
@@ -8785,11 +8798,11 @@
         <f>SUM(B32:B33)</f>
         <v/>
       </c>
-      <c r="C34" s="17">
+      <c r="C34" s="24">
         <f>SUM(C32:C33)</f>
         <v/>
       </c>
-      <c r="D34" s="18">
+      <c r="D34" s="25">
         <f>SUM(D32:D33)</f>
         <v/>
       </c>

--- a/AR-Sample-Ledger.xlsx
+++ b/AR-Sample-Ledger.xlsx
@@ -8,22 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haley/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8DA5E80C-7428-CA45-8E00-40CE58A04F54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CDD0F7AA-98D4-6C4A-B65B-049D445866B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Ledger" sheetId="2" r:id="rId1"/>
+    <sheet name="DATA" sheetId="2" r:id="rId1"/>
     <sheet name="About" sheetId="1" r:id="rId2"/>
     <sheet name="Calculations" sheetId="3" r:id="rId3"/>
     <sheet name="Aging pivot" sheetId="4" r:id="rId4"/>
     <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Ledger!$A$1:$R$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DATA!$A$1:$R$111</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -822,6 +821,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF1A355D"/>
+      <color rgb="FF99E3EB"/>
       <color rgb="FF1AD0FF"/>
       <color rgb="FF00FF7A"/>
       <color rgb="FFFFA975"/>
@@ -1957,7 +1958,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
-    <tabColor rgb="FF1B365D"/>
+    <tabColor rgb="FF1A355D"/>
   </sheetPr>
   <dimension ref="A1:R111"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -2101,7 +2102,7 @@
       </c>
       <c r="D3" s="6">
         <f ca="1">TODAY()+54</f>
-        <v>46366</v>
+        <v>46369</v>
       </c>
       <c r="E3" s="7">
         <v>53.4</v>
@@ -2379,7 +2380,7 @@
       </c>
       <c r="D8" s="6">
         <f ca="1">TODAY()+29</f>
-        <v>46341</v>
+        <v>46344</v>
       </c>
       <c r="E8" s="7">
         <v>95</v>
@@ -2932,7 +2933,7 @@
       </c>
       <c r="D18" s="6">
         <f ca="1">TODAY()+29</f>
-        <v>46341</v>
+        <v>46344</v>
       </c>
       <c r="E18" s="7">
         <v>40.049999999999997</v>
@@ -3045,7 +3046,7 @@
       </c>
       <c r="D20" s="6">
         <f ca="1">TODAY()+23</f>
-        <v>46335</v>
+        <v>46338</v>
       </c>
       <c r="E20" s="7">
         <v>30</v>
@@ -3103,7 +3104,7 @@
       </c>
       <c r="D21" s="6">
         <f ca="1">TODAY()+29</f>
-        <v>46341</v>
+        <v>46344</v>
       </c>
       <c r="E21" s="7">
         <v>195</v>
@@ -3161,7 +3162,7 @@
       </c>
       <c r="D22" s="6">
         <f ca="1">TODAY()+20</f>
-        <v>46332</v>
+        <v>46335</v>
       </c>
       <c r="E22" s="7">
         <v>37</v>
@@ -3219,7 +3220,7 @@
       </c>
       <c r="D23" s="6">
         <f ca="1">TODAY()+59</f>
-        <v>46371</v>
+        <v>46374</v>
       </c>
       <c r="E23" s="7">
         <v>4</v>
@@ -3497,7 +3498,7 @@
       </c>
       <c r="D28" s="6">
         <f ca="1">TODAY()+41</f>
-        <v>46353</v>
+        <v>46356</v>
       </c>
       <c r="E28" s="7">
         <v>14</v>
@@ -3555,7 +3556,7 @@
       </c>
       <c r="D29" s="6">
         <f ca="1">TODAY()+10</f>
-        <v>46322</v>
+        <v>46325</v>
       </c>
       <c r="E29" s="7">
         <v>1431.34</v>
@@ -3723,7 +3724,7 @@
       </c>
       <c r="D32" s="6">
         <f ca="1">TODAY()+24</f>
-        <v>46336</v>
+        <v>46339</v>
       </c>
       <c r="E32" s="7">
         <v>2</v>
@@ -3946,7 +3947,7 @@
       </c>
       <c r="D36" s="6">
         <f ca="1">TODAY()+29</f>
-        <v>46341</v>
+        <v>46344</v>
       </c>
       <c r="E36" s="7">
         <v>233</v>
@@ -4114,7 +4115,7 @@
       </c>
       <c r="D39" s="6">
         <f ca="1">TODAY()+8</f>
-        <v>46320</v>
+        <v>46323</v>
       </c>
       <c r="E39" s="7">
         <v>16</v>
@@ -4337,7 +4338,7 @@
       </c>
       <c r="D43" s="6">
         <f ca="1">TODAY()+54</f>
-        <v>46366</v>
+        <v>46369</v>
       </c>
       <c r="E43" s="7">
         <v>30</v>
@@ -4505,7 +4506,7 @@
       </c>
       <c r="D46" s="6">
         <f ca="1">TODAY()+41</f>
-        <v>46353</v>
+        <v>46356</v>
       </c>
       <c r="E46" s="7">
         <v>30</v>
@@ -4563,7 +4564,7 @@
       </c>
       <c r="D47" s="6">
         <f ca="1">TODAY()+10</f>
-        <v>46322</v>
+        <v>46325</v>
       </c>
       <c r="E47" s="7">
         <v>108.6</v>
@@ -4786,7 +4787,7 @@
       </c>
       <c r="D51" s="6">
         <f ca="1">TODAY()+65</f>
-        <v>46377</v>
+        <v>46380</v>
       </c>
       <c r="E51" s="7">
         <v>50</v>
@@ -5119,7 +5120,7 @@
       </c>
       <c r="D57" s="6">
         <f ca="1">TODAY()+23</f>
-        <v>46335</v>
+        <v>46338</v>
       </c>
       <c r="E57" s="7">
         <v>30.6</v>
@@ -5342,7 +5343,7 @@
       </c>
       <c r="D61" s="6">
         <f ca="1">TODAY()+62</f>
-        <v>46374</v>
+        <v>46377</v>
       </c>
       <c r="E61" s="7">
         <v>107</v>
@@ -5400,7 +5401,7 @@
       </c>
       <c r="D62" s="6">
         <f ca="1">TODAY()+18</f>
-        <v>46330</v>
+        <v>46333</v>
       </c>
       <c r="E62" s="7">
         <v>357</v>
@@ -5568,7 +5569,7 @@
       </c>
       <c r="D65" s="6">
         <f ca="1">TODAY()+36</f>
-        <v>46348</v>
+        <v>46351</v>
       </c>
       <c r="E65" s="7">
         <v>116</v>
@@ -5791,7 +5792,7 @@
       </c>
       <c r="D69" s="6">
         <f ca="1">TODAY()+70</f>
-        <v>46382</v>
+        <v>46385</v>
       </c>
       <c r="E69" s="7">
         <v>50</v>
@@ -5849,7 +5850,7 @@
       </c>
       <c r="D70" s="6">
         <f ca="1">TODAY()+31</f>
-        <v>46343</v>
+        <v>46346</v>
       </c>
       <c r="E70" s="7">
         <v>20.8</v>
@@ -5962,7 +5963,7 @@
       </c>
       <c r="D72" s="6">
         <f ca="1">TODAY()+10</f>
-        <v>46322</v>
+        <v>46325</v>
       </c>
       <c r="E72" s="7">
         <v>311</v>
@@ -6130,7 +6131,7 @@
       </c>
       <c r="D75" s="6">
         <f ca="1">TODAY()+23</f>
-        <v>46335</v>
+        <v>46338</v>
       </c>
       <c r="E75" s="7">
         <v>208</v>
@@ -6188,7 +6189,7 @@
       </c>
       <c r="D76" s="6">
         <f ca="1">TODAY()+17</f>
-        <v>46329</v>
+        <v>46332</v>
       </c>
       <c r="E76" s="7">
         <v>30</v>
@@ -6246,7 +6247,7 @@
       </c>
       <c r="D77" s="6">
         <f ca="1">TODAY()+42</f>
-        <v>46354</v>
+        <v>46357</v>
       </c>
       <c r="E77" s="7">
         <v>3180</v>
@@ -6689,7 +6690,7 @@
       </c>
       <c r="D85" s="6">
         <f ca="1">TODAY()+37</f>
-        <v>46349</v>
+        <v>46352</v>
       </c>
       <c r="E85" s="7">
         <v>208</v>
@@ -6802,7 +6803,7 @@
       </c>
       <c r="D87" s="6">
         <f ca="1">TODAY()+10</f>
-        <v>46322</v>
+        <v>46325</v>
       </c>
       <c r="E87" s="7">
         <v>10.5</v>
@@ -7025,7 +7026,7 @@
       </c>
       <c r="D91" s="6">
         <f ca="1">TODAY()+28</f>
-        <v>46340</v>
+        <v>46343</v>
       </c>
       <c r="E91" s="7">
         <v>21.2</v>
@@ -7138,7 +7139,7 @@
       </c>
       <c r="D93" s="6">
         <f ca="1">TODAY()+41</f>
-        <v>46353</v>
+        <v>46356</v>
       </c>
       <c r="E93" s="7">
         <v>117</v>
@@ -7196,7 +7197,7 @@
       </c>
       <c r="D94" s="6">
         <f ca="1">TODAY()+14</f>
-        <v>46326</v>
+        <v>46329</v>
       </c>
       <c r="E94" s="7">
         <v>28.6</v>
@@ -7584,7 +7585,7 @@
       </c>
       <c r="D101" s="6">
         <f ca="1">TODAY()+64</f>
-        <v>46376</v>
+        <v>46379</v>
       </c>
       <c r="E101" s="7">
         <v>59.6</v>
@@ -7642,7 +7643,7 @@
       </c>
       <c r="D102" s="6">
         <f ca="1">TODAY()+59</f>
-        <v>46371</v>
+        <v>46374</v>
       </c>
       <c r="E102" s="7">
         <v>1549</v>
@@ -7810,7 +7811,7 @@
       </c>
       <c r="D105" s="6">
         <f ca="1">TODAY()+66</f>
-        <v>46378</v>
+        <v>46381</v>
       </c>
       <c r="E105" s="7">
         <v>49.8</v>
@@ -7868,7 +7869,7 @@
       </c>
       <c r="D106" s="6">
         <f ca="1">TODAY()+47</f>
-        <v>46359</v>
+        <v>46362</v>
       </c>
       <c r="E106" s="7">
         <v>21.8</v>
@@ -7981,7 +7982,7 @@
       </c>
       <c r="D108" s="6">
         <f ca="1">TODAY()+63</f>
-        <v>46375</v>
+        <v>46378</v>
       </c>
       <c r="E108" s="7">
         <v>30</v>
@@ -8039,7 +8040,7 @@
       </c>
       <c r="D109" s="6">
         <f ca="1">TODAY()+15</f>
-        <v>46327</v>
+        <v>46330</v>
       </c>
       <c r="E109" s="7">
         <v>51</v>
@@ -8097,7 +8098,7 @@
       </c>
       <c r="D110" s="6">
         <f ca="1">TODAY()+11</f>
-        <v>46323</v>
+        <v>46326</v>
       </c>
       <c r="E110" s="7">
         <v>69</v>
@@ -8155,7 +8156,7 @@
       </c>
       <c r="D111" s="6">
         <f ca="1">TODAY()+13</f>
-        <v>46325</v>
+        <v>46328</v>
       </c>
       <c r="E111" s="7">
         <v>27.5</v>
@@ -8214,6 +8215,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <tabColor theme="0"/>
+  </sheetPr>
   <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -8326,7 +8330,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
-    <tabColor rgb="FF294BEF"/>
+    <tabColor rgb="FF1A355D"/>
   </sheetPr>
   <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -8356,7 +8360,7 @@
         <v>172</v>
       </c>
       <c r="B4">
-        <f>COUNTA(Ledger!B2:B111)</f>
+        <f>COUNTA(DATA!B2:B111)</f>
         <v>110</v>
       </c>
     </row>
@@ -8365,7 +8369,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="12">
-        <f>SUM(Ledger!E2:E111)</f>
+        <f>SUM(DATA!E2:E111)</f>
         <v>22550.509999999991</v>
       </c>
     </row>
@@ -8374,7 +8378,7 @@
         <v>173</v>
       </c>
       <c r="B6" s="12">
-        <f>SUM(Ledger!F2:F111)</f>
+        <f>SUM(DATA!F2:F111)</f>
         <v>20022.139999999996</v>
       </c>
     </row>
@@ -8383,7 +8387,7 @@
         <v>174</v>
       </c>
       <c r="B7" s="12">
-        <f>SUM(Ledger!G2:G111)</f>
+        <f>SUM(DATA!G2:G111)</f>
         <v>2528.37</v>
       </c>
     </row>
@@ -8401,7 +8405,7 @@
         <v>11</v>
       </c>
       <c r="B9" s="12">
-        <f>SUM(Ledger!K2:K111)</f>
+        <f>SUM(DATA!K2:K111)</f>
         <v>20022.139999999996</v>
       </c>
     </row>
@@ -8419,7 +8423,7 @@
         <v>177</v>
       </c>
       <c r="B11">
-        <f>COUNTIF(Ledger!K2:K111,"&gt;0")</f>
+        <f>COUNTIF(DATA!K2:K111,"&gt;0")</f>
         <v>109</v>
       </c>
     </row>
@@ -8428,7 +8432,7 @@
         <v>178</v>
       </c>
       <c r="B12">
-        <f>COUNTIFS(Ledger!K2:K111,"&gt;0",Ledger!Q2:Q111,"No")</f>
+        <f>COUNTIFS(DATA!K2:K111,"&gt;0",DATA!Q2:Q111,"No")</f>
         <v>71</v>
       </c>
     </row>
@@ -8437,7 +8441,7 @@
         <v>179</v>
       </c>
       <c r="B13" s="14">
-        <f>SUMPRODUCT(1/COUNTIF(Ledger!A2:A111,Ledger!A2:A111))</f>
+        <f>SUMPRODUCT(1/COUNTIF(DATA!A2:A111,DATA!A2:A111))</f>
         <v>59.000000000000028</v>
       </c>
     </row>
@@ -8468,11 +8472,11 @@
         <v>186</v>
       </c>
       <c r="B17" s="12">
-        <f>SUM(Ledger!H2:H111)</f>
+        <f>SUM(DATA!H2:H111)</f>
         <v>0</v>
       </c>
       <c r="C17" s="12">
-        <f>SUM(Ledger!L2:L111)</f>
+        <f>SUM(DATA!L2:L111)</f>
         <v>0</v>
       </c>
       <c r="D17" s="12">
@@ -8489,11 +8493,11 @@
         <v>187</v>
       </c>
       <c r="B18" s="12">
-        <f>SUM(Ledger!I2:I111)</f>
+        <f>SUM(DATA!I2:I111)</f>
         <v>0</v>
       </c>
       <c r="C18" s="12">
-        <f>SUM(Ledger!M2:M111)</f>
+        <f>SUM(DATA!M2:M111)</f>
         <v>0</v>
       </c>
       <c r="D18" s="12">
@@ -8510,11 +8514,11 @@
         <v>188</v>
       </c>
       <c r="B19" s="12">
-        <f>SUM(Ledger!J2:J111)</f>
+        <f>SUM(DATA!J2:J111)</f>
         <v>0</v>
       </c>
       <c r="C19" s="12">
-        <f>SUM(Ledger!N2:N111)</f>
+        <f>SUM(DATA!N2:N111)</f>
         <v>0</v>
       </c>
       <c r="D19" s="12">
@@ -8531,11 +8535,11 @@
         <v>21</v>
       </c>
       <c r="B20" s="12">
-        <f>SUM(Ledger!K2:K111)</f>
+        <f>SUM(DATA!K2:K111)</f>
         <v>20022.139999999996</v>
       </c>
       <c r="C20" s="12">
-        <f>SUM(Ledger!O2:O111)</f>
+        <f>SUM(DATA!O2:O111)</f>
         <v>2528.37</v>
       </c>
       <c r="D20" s="12">
@@ -8587,7 +8591,7 @@
         <v>192</v>
       </c>
       <c r="B25" s="12">
-        <f>SUMIFS(Ledger!E2:E111,Ledger!K2:K111,"&gt;0",Ledger!Q2:Q111,"No")</f>
+        <f>SUMIFS(DATA!E2:E111,DATA!K2:K111,"&gt;0",DATA!Q2:Q111,"No")</f>
         <v>13527.720000000003</v>
       </c>
     </row>
@@ -8602,7 +8606,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
-    <tabColor rgb="FFFF88CF"/>
+    <tabColor theme="0"/>
   </sheetPr>
   <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -8647,19 +8651,19 @@
         <v>186</v>
       </c>
       <c r="B5" s="12">
-        <f>SUMIF(Ledger!P:P,A5,Ledger!F:F)</f>
+        <f>SUMIF(DATA!P:P,A5,DATA!F:F)</f>
         <v>0</v>
       </c>
       <c r="C5" s="12">
-        <f>SUMIF(Ledger!P:P,A5,Ledger!G:G)</f>
+        <f>SUMIF(DATA!P:P,A5,DATA!G:G)</f>
         <v>0</v>
       </c>
       <c r="D5">
-        <f>COUNTIF(Ledger!P:P,A5)</f>
+        <f>COUNTIF(DATA!P:P,A5)</f>
         <v>0</v>
       </c>
       <c r="E5">
-        <f>COUNTIFS(Ledger!P:P,A5,Ledger!Q:Q,"No")</f>
+        <f>COUNTIFS(DATA!P:P,A5,DATA!Q:Q,"No")</f>
         <v>0</v>
       </c>
     </row>
@@ -8668,19 +8672,19 @@
         <v>187</v>
       </c>
       <c r="B6" s="12">
-        <f>SUMIF(Ledger!P:P,A6,Ledger!F:F)</f>
+        <f>SUMIF(DATA!P:P,A6,DATA!F:F)</f>
         <v>0</v>
       </c>
       <c r="C6" s="12">
-        <f>SUMIF(Ledger!P:P,A6,Ledger!G:G)</f>
+        <f>SUMIF(DATA!P:P,A6,DATA!G:G)</f>
         <v>0</v>
       </c>
       <c r="D6">
-        <f>COUNTIF(Ledger!P:P,A6)</f>
+        <f>COUNTIF(DATA!P:P,A6)</f>
         <v>0</v>
       </c>
       <c r="E6">
-        <f>COUNTIFS(Ledger!P:P,A6,Ledger!Q:Q,"No")</f>
+        <f>COUNTIFS(DATA!P:P,A6,DATA!Q:Q,"No")</f>
         <v>0</v>
       </c>
     </row>
@@ -8689,19 +8693,19 @@
         <v>188</v>
       </c>
       <c r="B7" s="12">
-        <f>SUMIF(Ledger!P:P,A7,Ledger!F:F)</f>
+        <f>SUMIF(DATA!P:P,A7,DATA!F:F)</f>
         <v>0</v>
       </c>
       <c r="C7" s="12">
-        <f>SUMIF(Ledger!P:P,A7,Ledger!G:G)</f>
+        <f>SUMIF(DATA!P:P,A7,DATA!G:G)</f>
         <v>0</v>
       </c>
       <c r="D7">
-        <f>COUNTIF(Ledger!P:P,A7)</f>
+        <f>COUNTIF(DATA!P:P,A7)</f>
         <v>0</v>
       </c>
       <c r="E7">
-        <f>COUNTIFS(Ledger!P:P,A7,Ledger!Q:Q,"No")</f>
+        <f>COUNTIFS(DATA!P:P,A7,DATA!Q:Q,"No")</f>
         <v>0</v>
       </c>
     </row>
@@ -8710,19 +8714,19 @@
         <v>21</v>
       </c>
       <c r="B8" s="12">
-        <f>SUMIF(Ledger!P:P,A8,Ledger!F:F)</f>
+        <f>SUMIF(DATA!P:P,A8,DATA!F:F)</f>
         <v>20022.139999999996</v>
       </c>
       <c r="C8" s="12">
-        <f>SUMIF(Ledger!P:P,A8,Ledger!G:G)</f>
+        <f>SUMIF(DATA!P:P,A8,DATA!G:G)</f>
         <v>2528.37</v>
       </c>
       <c r="D8">
-        <f>COUNTIF(Ledger!P:P,A8)</f>
+        <f>COUNTIF(DATA!P:P,A8)</f>
         <v>110</v>
       </c>
       <c r="E8">
-        <f>COUNTIFS(Ledger!P:P,A8,Ledger!Q:Q,"No")</f>
+        <f>COUNTIFS(DATA!P:P,A8,DATA!Q:Q,"No")</f>
         <v>71</v>
       </c>
     </row>
@@ -8776,15 +8780,15 @@
         <v>98</v>
       </c>
       <c r="B14" s="12">
-        <f>SUMIF(Ledger!A:A,A14,Ledger!E:E)</f>
+        <f>SUMIF(DATA!A:A,A14,DATA!E:E)</f>
         <v>4115.32</v>
       </c>
       <c r="C14" s="12">
-        <f>SUMIF(Ledger!A:A,A14,Ledger!F:F)</f>
+        <f>SUMIF(DATA!A:A,A14,DATA!F:F)</f>
         <v>3660.32</v>
       </c>
       <c r="D14" s="12">
-        <f>SUMIF(Ledger!A:A,A14,Ledger!G:G)</f>
+        <f>SUMIF(DATA!A:A,A14,DATA!G:G)</f>
         <v>455</v>
       </c>
     </row>
@@ -8793,15 +8797,15 @@
         <v>118</v>
       </c>
       <c r="B15" s="12">
-        <f>SUMIF(Ledger!A:A,A15,Ledger!E:E)</f>
+        <f>SUMIF(DATA!A:A,A15,DATA!E:E)</f>
         <v>3180</v>
       </c>
       <c r="C15" s="12">
-        <f>SUMIF(Ledger!A:A,A15,Ledger!F:F)</f>
+        <f>SUMIF(DATA!A:A,A15,DATA!F:F)</f>
         <v>3180</v>
       </c>
       <c r="D15" s="12">
-        <f>SUMIF(Ledger!A:A,A15,Ledger!G:G)</f>
+        <f>SUMIF(DATA!A:A,A15,DATA!G:G)</f>
         <v>0</v>
       </c>
     </row>
@@ -8810,15 +8814,15 @@
         <v>156</v>
       </c>
       <c r="B16" s="12">
-        <f>SUMIF(Ledger!A:A,A16,Ledger!E:E)</f>
+        <f>SUMIF(DATA!A:A,A16,DATA!E:E)</f>
         <v>2735.6</v>
       </c>
       <c r="C16" s="12">
-        <f>SUMIF(Ledger!A:A,A16,Ledger!F:F)</f>
+        <f>SUMIF(DATA!A:A,A16,DATA!F:F)</f>
         <v>1880.6</v>
       </c>
       <c r="D16" s="12">
-        <f>SUMIF(Ledger!A:A,A16,Ledger!G:G)</f>
+        <f>SUMIF(DATA!A:A,A16,DATA!G:G)</f>
         <v>855</v>
       </c>
     </row>
@@ -8827,15 +8831,15 @@
         <v>71</v>
       </c>
       <c r="B17" s="12">
-        <f>SUMIF(Ledger!A:A,A17,Ledger!E:E)</f>
+        <f>SUMIF(DATA!A:A,A17,DATA!E:E)</f>
         <v>2226.15</v>
       </c>
       <c r="C17" s="12">
-        <f>SUMIF(Ledger!A:A,A17,Ledger!F:F)</f>
+        <f>SUMIF(DATA!A:A,A17,DATA!F:F)</f>
         <v>1228.78</v>
       </c>
       <c r="D17" s="12">
-        <f>SUMIF(Ledger!A:A,A17,Ledger!G:G)</f>
+        <f>SUMIF(DATA!A:A,A17,DATA!G:G)</f>
         <v>997.37</v>
       </c>
     </row>
@@ -8844,15 +8848,15 @@
         <v>59</v>
       </c>
       <c r="B18" s="12">
-        <f>SUMIF(Ledger!A:A,A18,Ledger!E:E)</f>
+        <f>SUMIF(DATA!A:A,A18,DATA!E:E)</f>
         <v>1880.9399999999998</v>
       </c>
       <c r="C18" s="12">
-        <f>SUMIF(Ledger!A:A,A18,Ledger!F:F)</f>
+        <f>SUMIF(DATA!A:A,A18,DATA!F:F)</f>
         <v>1659.9399999999998</v>
       </c>
       <c r="D18" s="12">
-        <f>SUMIF(Ledger!A:A,A18,Ledger!G:G)</f>
+        <f>SUMIF(DATA!A:A,A18,DATA!G:G)</f>
         <v>221</v>
       </c>
     </row>
@@ -8861,15 +8865,15 @@
         <v>80</v>
       </c>
       <c r="B19" s="12">
-        <f>SUMIF(Ledger!A:A,A19,Ledger!E:E)</f>
+        <f>SUMIF(DATA!A:A,A19,DATA!E:E)</f>
         <v>1350</v>
       </c>
       <c r="C19" s="12">
-        <f>SUMIF(Ledger!A:A,A19,Ledger!F:F)</f>
+        <f>SUMIF(DATA!A:A,A19,DATA!F:F)</f>
         <v>1350</v>
       </c>
       <c r="D19" s="12">
-        <f>SUMIF(Ledger!A:A,A19,Ledger!G:G)</f>
+        <f>SUMIF(DATA!A:A,A19,DATA!G:G)</f>
         <v>0</v>
       </c>
     </row>
@@ -8878,15 +8882,15 @@
         <v>89</v>
       </c>
       <c r="B20" s="12">
-        <f>SUMIF(Ledger!A:A,A20,Ledger!E:E)</f>
+        <f>SUMIF(DATA!A:A,A20,DATA!E:E)</f>
         <v>975.1</v>
       </c>
       <c r="C20" s="12">
-        <f>SUMIF(Ledger!A:A,A20,Ledger!F:F)</f>
+        <f>SUMIF(DATA!A:A,A20,DATA!F:F)</f>
         <v>975.1</v>
       </c>
       <c r="D20" s="12">
-        <f>SUMIF(Ledger!A:A,A20,Ledger!G:G)</f>
+        <f>SUMIF(DATA!A:A,A20,DATA!G:G)</f>
         <v>0</v>
       </c>
     </row>
@@ -8895,15 +8899,15 @@
         <v>32</v>
       </c>
       <c r="B21" s="12">
-        <f>SUMIF(Ledger!A:A,A21,Ledger!E:E)</f>
+        <f>SUMIF(DATA!A:A,A21,DATA!E:E)</f>
         <v>523</v>
       </c>
       <c r="C21" s="12">
-        <f>SUMIF(Ledger!A:A,A21,Ledger!F:F)</f>
+        <f>SUMIF(DATA!A:A,A21,DATA!F:F)</f>
         <v>523</v>
       </c>
       <c r="D21" s="12">
-        <f>SUMIF(Ledger!A:A,A21,Ledger!G:G)</f>
+        <f>SUMIF(DATA!A:A,A21,DATA!G:G)</f>
         <v>0</v>
       </c>
     </row>
@@ -8912,15 +8916,15 @@
         <v>42</v>
       </c>
       <c r="B22" s="12">
-        <f>SUMIF(Ledger!A:A,A22,Ledger!E:E)</f>
+        <f>SUMIF(DATA!A:A,A22,DATA!E:E)</f>
         <v>521.45000000000005</v>
       </c>
       <c r="C22" s="12">
-        <f>SUMIF(Ledger!A:A,A22,Ledger!F:F)</f>
+        <f>SUMIF(DATA!A:A,A22,DATA!F:F)</f>
         <v>521.45000000000005</v>
       </c>
       <c r="D22" s="12">
-        <f>SUMIF(Ledger!A:A,A22,Ledger!G:G)</f>
+        <f>SUMIF(DATA!A:A,A22,DATA!G:G)</f>
         <v>0</v>
       </c>
     </row>
@@ -8929,15 +8933,15 @@
         <v>64</v>
       </c>
       <c r="B23" s="12">
-        <f>SUMIF(Ledger!A:A,A23,Ledger!E:E)</f>
+        <f>SUMIF(DATA!A:A,A23,DATA!E:E)</f>
         <v>459.55</v>
       </c>
       <c r="C23" s="12">
-        <f>SUMIF(Ledger!A:A,A23,Ledger!F:F)</f>
+        <f>SUMIF(DATA!A:A,A23,DATA!F:F)</f>
         <v>459.55</v>
       </c>
       <c r="D23" s="12">
-        <f>SUMIF(Ledger!A:A,A23,Ledger!G:G)</f>
+        <f>SUMIF(DATA!A:A,A23,DATA!G:G)</f>
         <v>0</v>
       </c>
     </row>
@@ -8946,15 +8950,15 @@
         <v>37</v>
       </c>
       <c r="B24" s="12">
-        <f>SUMIF(Ledger!A:A,A24,Ledger!E:E)</f>
+        <f>SUMIF(DATA!A:A,A24,DATA!E:E)</f>
         <v>440.5</v>
       </c>
       <c r="C24" s="12">
-        <f>SUMIF(Ledger!A:A,A24,Ledger!F:F)</f>
+        <f>SUMIF(DATA!A:A,A24,DATA!F:F)</f>
         <v>440.5</v>
       </c>
       <c r="D24" s="12">
-        <f>SUMIF(Ledger!A:A,A24,Ledger!G:G)</f>
+        <f>SUMIF(DATA!A:A,A24,DATA!G:G)</f>
         <v>0</v>
       </c>
     </row>
@@ -8963,15 +8967,15 @@
         <v>129</v>
       </c>
       <c r="B25" s="12">
-        <f>SUMIF(Ledger!A:A,A25,Ledger!E:E)</f>
+        <f>SUMIF(DATA!A:A,A25,DATA!E:E)</f>
         <v>339</v>
       </c>
       <c r="C25" s="12">
-        <f>SUMIF(Ledger!A:A,A25,Ledger!F:F)</f>
+        <f>SUMIF(DATA!A:A,A25,DATA!F:F)</f>
         <v>339</v>
       </c>
       <c r="D25" s="12">
-        <f>SUMIF(Ledger!A:A,A25,Ledger!G:G)</f>
+        <f>SUMIF(DATA!A:A,A25,DATA!G:G)</f>
         <v>0</v>
       </c>
     </row>
@@ -8980,15 +8984,15 @@
         <v>113</v>
       </c>
       <c r="B26" s="12">
-        <f>SUMIF(Ledger!A:A,A26,Ledger!E:E)</f>
+        <f>SUMIF(DATA!A:A,A26,DATA!E:E)</f>
         <v>332.8</v>
       </c>
       <c r="C26" s="12">
-        <f>SUMIF(Ledger!A:A,A26,Ledger!F:F)</f>
+        <f>SUMIF(DATA!A:A,A26,DATA!F:F)</f>
         <v>332.8</v>
       </c>
       <c r="D26" s="12">
-        <f>SUMIF(Ledger!A:A,A26,Ledger!G:G)</f>
+        <f>SUMIF(DATA!A:A,A26,DATA!G:G)</f>
         <v>0</v>
       </c>
     </row>
@@ -8997,15 +9001,15 @@
         <v>87</v>
       </c>
       <c r="B27" s="12">
-        <f>SUMIF(Ledger!A:A,A27,Ledger!E:E)</f>
+        <f>SUMIF(DATA!A:A,A27,DATA!E:E)</f>
         <v>277</v>
       </c>
       <c r="C27" s="12">
-        <f>SUMIF(Ledger!A:A,A27,Ledger!F:F)</f>
+        <f>SUMIF(DATA!A:A,A27,DATA!F:F)</f>
         <v>277</v>
       </c>
       <c r="D27" s="12">
-        <f>SUMIF(Ledger!A:A,A27,Ledger!G:G)</f>
+        <f>SUMIF(DATA!A:A,A27,DATA!G:G)</f>
         <v>0</v>
       </c>
     </row>
@@ -9014,15 +9018,15 @@
         <v>51</v>
       </c>
       <c r="B28" s="12">
-        <f>SUMIF(Ledger!A:A,A28,Ledger!E:E)</f>
+        <f>SUMIF(DATA!A:A,A28,DATA!E:E)</f>
         <v>272.7</v>
       </c>
       <c r="C28" s="12">
-        <f>SUMIF(Ledger!A:A,A28,Ledger!F:F)</f>
+        <f>SUMIF(DATA!A:A,A28,DATA!F:F)</f>
         <v>272.7</v>
       </c>
       <c r="D28" s="12">
-        <f>SUMIF(Ledger!A:A,A28,Ledger!G:G)</f>
+        <f>SUMIF(DATA!A:A,A28,DATA!G:G)</f>
         <v>0</v>
       </c>
     </row>
@@ -9050,11 +9054,11 @@
         <v>198</v>
       </c>
       <c r="B32">
-        <f>COUNTIF(Ledger!Q2:Q111,"Yes")</f>
+        <f>COUNTIF(DATA!Q2:Q111,"Yes")</f>
         <v>39</v>
       </c>
       <c r="C32" s="12">
-        <f>SUMIF(Ledger!Q2:Q111,"Yes",Ledger!E2:E111)</f>
+        <f>SUMIF(DATA!Q2:Q111,"Yes",DATA!E2:E111)</f>
         <v>9022.7899999999991</v>
       </c>
       <c r="D32" s="13">
@@ -9067,11 +9071,11 @@
         <v>199</v>
       </c>
       <c r="B33">
-        <f>COUNTIF(Ledger!Q2:Q111,"No")</f>
+        <f>COUNTIF(DATA!Q2:Q111,"No")</f>
         <v>71</v>
       </c>
       <c r="C33" s="12">
-        <f>SUMIF(Ledger!Q2:Q111,"No",Ledger!E2:E111)</f>
+        <f>SUMIF(DATA!Q2:Q111,"No",DATA!E2:E111)</f>
         <v>13527.720000000003</v>
       </c>
       <c r="D33" s="13">
